--- a/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
+++ b/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
@@ -11,6 +11,7 @@
     <sheet name="1 Month" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="12 Month" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Per-Slip Detail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="คู่มือ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -106,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -128,11 +129,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -146,7 +191,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -202,6 +248,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -610,45 +662,69 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
       <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>รายการ</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>ราคา/สลิป</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>หน่วย</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ราคาขาย MOU (flat ทุก tier)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="9" t="n">
         <v>0.125</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>บาท/สลิป</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -660,81 +736,81 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>ต้นทุน/สลิป</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>GP/สลิป</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>GP %</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>เรทคอมแนะนำ</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Net margin หลังคอม</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>A — Other-source 100%</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="13" t="n">
         <v>0.11</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="13" t="n">
         <v>0.015</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="14" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>B — Mix blend (~30/70)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>0.077</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>0.048</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.384</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>0.304</v>
       </c>
     </row>
@@ -748,15 +824,15 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="F13" s="6" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Scenario A (cost 0.11)</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>margin บางมาก (12%) → ให้คอม 3% revenue บริษัทเหลือ ~9% รองรับ opex ได้</t>
         </is>
@@ -764,15 +840,15 @@
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Scenario B (cost 0.077)</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>margin หนา (38.4%) → ให้คอม 8% revenue ได้ บริษัทเหลือ ~30% เซลส์ได้แรง</t>
         </is>
@@ -780,15 +856,15 @@
       <c r="C15" s="5" t="n"/>
       <c r="D15" s="5" t="n"/>
       <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ทางเลือก: คิดเป็น % ของ GP</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>A @ 25% ของ GP ≈ 3% revenue · B @ 20% ของ GP ≈ 7.7% revenue</t>
         </is>
@@ -796,15 +872,15 @@
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ข้อระวัง MOU</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>ถ้าใช้ Scenario B ต้อง lock traffic mix ใน MOU (เช่น K-src ≥ 30%)</t>
         </is>
@@ -812,7 +888,7 @@
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -880,7 +956,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="6" t="n"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO A — ต้นทุน 0.11 บ./สลิป</t>
@@ -888,7 +964,7 @@
       </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO B — ต้นทุน 0.077 บ./สลิป</t>
@@ -896,469 +972,469 @@
       </c>
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Slips/1 Month</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Price/1 Month</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Comm @3%</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Net GP</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Comm @8%</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Net GP</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Coperate A</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>12500</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>11000</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>375</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <v>1125</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="21" t="n">
         <v>7700</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="21" t="n">
         <v>4800</v>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="21" t="n">
         <v>1000</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="21" t="n">
         <v>3800</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Coperate B</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>200000</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>25000</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>22000</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>750</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <v>2250</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="21" t="n">
         <v>15400</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="21" t="n">
         <v>9600</v>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="21" t="n">
         <v>2000</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="21" t="n">
         <v>7600</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Coperate C</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>300000</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>37500</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>33000</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>4500</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <v>1125</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="20" t="n">
         <v>3375</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="21" t="n">
         <v>23100</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="21" t="n">
         <v>14400</v>
       </c>
-      <c r="J8" s="20" t="n">
+      <c r="J8" s="21" t="n">
         <v>3000</v>
       </c>
-      <c r="K8" s="20" t="n">
+      <c r="K8" s="21" t="n">
         <v>11400</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Coperate D</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>400000</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>50000</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>44000</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>6000</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>1500</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <v>4500</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>30800</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="21" t="n">
         <v>19200</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="21" t="n">
         <v>4000</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K9" s="21" t="n">
         <v>15200</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Coperate E</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>500000</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="19" t="n">
         <v>62500</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>55000</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>7500</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>1875</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>5625</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="21" t="n">
         <v>38500</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="21" t="n">
         <v>24000</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="J10" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="K10" s="21" t="n">
         <v>19000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Coperate F</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>600000</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>66000</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>9000</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>2250</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>6750</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>46200</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="21" t="n">
         <v>28800</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="21" t="n">
         <v>6000</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="21" t="n">
         <v>22800</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Coperate G</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>700000</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>87500</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>77000</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>10500</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>2625</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>7875</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <v>53900</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="21" t="n">
         <v>33600</v>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="21" t="n">
         <v>7000</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="21" t="n">
         <v>26600</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Coperate H</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>800000</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>100000</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="20" t="n">
         <v>88000</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="20" t="n">
         <v>12000</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="20" t="n">
         <v>9000</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="21" t="n">
         <v>61600</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="21" t="n">
         <v>38400</v>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="21" t="n">
         <v>8000</v>
       </c>
-      <c r="K13" s="20" t="n">
+      <c r="K13" s="21" t="n">
         <v>30400</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Coperate I</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>900000</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>112500</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="20" t="n">
         <v>99000</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="20" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <v>3375</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="20" t="n">
         <v>10125</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="21" t="n">
         <v>69300</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="21" t="n">
         <v>43200</v>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="J14" s="21" t="n">
         <v>9000</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="K14" s="21" t="n">
         <v>34200</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Coperate J</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>1000000</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>125000</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="20" t="n">
         <v>110000</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="20" t="n">
         <v>15000</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>3750</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <v>11250</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="21" t="n">
         <v>77000</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="21" t="n">
         <v>48000</v>
       </c>
-      <c r="J15" s="20" t="n">
+      <c r="J15" s="21" t="n">
         <v>10000</v>
       </c>
-      <c r="K15" s="20" t="n">
+      <c r="K15" s="21" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>5500000</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>687500</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>605000</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <v>82500</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>20625</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="23" t="n">
         <v>61875</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="23" t="n">
         <v>423500</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="23" t="n">
         <v>264000</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="23" t="n">
         <v>55000</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="23" t="n">
         <v>209000</v>
       </c>
     </row>
@@ -1424,7 +1500,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="6" t="n"/>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO A — ต้นทุน 0.11 บ./สลิป</t>
@@ -1432,7 +1508,7 @@
       </c>
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO B — ต้นทุน 0.077 บ./สลิป</t>
@@ -1440,469 +1516,469 @@
       </c>
       <c r="I4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Slips/12 Month</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Price/12 Month</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Comm @3%</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Net GP</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>GP</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>Comm @8%</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Net GP</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Coperate A</t>
         </is>
       </c>
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="19" t="n">
         <v>1200000</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>150000</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <v>132000</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="20" t="n">
         <v>18000</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="20" t="n">
         <v>4500</v>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="20" t="n">
         <v>13500</v>
       </c>
-      <c r="H6" s="20" t="n">
+      <c r="H6" s="21" t="n">
         <v>92400</v>
       </c>
-      <c r="I6" s="20" t="n">
+      <c r="I6" s="21" t="n">
         <v>57600</v>
       </c>
-      <c r="J6" s="20" t="n">
+      <c r="J6" s="21" t="n">
         <v>12000</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="21" t="n">
         <v>45600</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Coperate B</t>
         </is>
       </c>
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="19" t="n">
         <v>2400000</v>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>300000</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="20" t="n">
         <v>264000</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="20" t="n">
         <v>36000</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="20" t="n">
         <v>9000</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="20" t="n">
         <v>27000</v>
       </c>
-      <c r="H7" s="20" t="n">
+      <c r="H7" s="21" t="n">
         <v>184800</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="21" t="n">
         <v>115200</v>
       </c>
-      <c r="J7" s="20" t="n">
+      <c r="J7" s="21" t="n">
         <v>24000</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="21" t="n">
         <v>91200</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Coperate C</t>
         </is>
       </c>
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="19" t="n">
         <v>3600000</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>450000</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>396000</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>54000</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="20" t="n">
         <v>13500</v>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="20" t="n">
         <v>40500</v>
       </c>
-      <c r="H8" s="20" t="n">
+      <c r="H8" s="21" t="n">
         <v>277200</v>
       </c>
-      <c r="I8" s="20" t="n">
+      <c r="I8" s="21" t="n">
         <v>172800</v>
       </c>
-      <c r="J8" s="20" t="n">
+      <c r="J8" s="21" t="n">
         <v>36000</v>
       </c>
-      <c r="K8" s="20" t="n">
+      <c r="K8" s="21" t="n">
         <v>136800</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Coperate D</t>
         </is>
       </c>
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="19" t="n">
         <v>4800000</v>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="19" t="n">
         <v>600000</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>528000</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>72000</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="20" t="n">
         <v>18000</v>
       </c>
-      <c r="G9" s="19" t="n">
+      <c r="G9" s="20" t="n">
         <v>54000</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="21" t="n">
         <v>369600</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="21" t="n">
         <v>230400</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="21" t="n">
         <v>48000</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K9" s="21" t="n">
         <v>182400</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Coperate E</t>
         </is>
       </c>
-      <c r="B10" s="18" t="n">
+      <c r="B10" s="19" t="n">
         <v>6000000</v>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="19" t="n">
         <v>750000</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>660000</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>90000</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="20" t="n">
         <v>22500</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G10" s="20" t="n">
         <v>67500</v>
       </c>
-      <c r="H10" s="20" t="n">
+      <c r="H10" s="21" t="n">
         <v>462000</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="21" t="n">
         <v>288000</v>
       </c>
-      <c r="J10" s="20" t="n">
+      <c r="J10" s="21" t="n">
         <v>60000</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="K10" s="21" t="n">
         <v>228000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Coperate F</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="19" t="n">
         <v>7200000</v>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="19" t="n">
         <v>900000</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>792000</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>108000</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="20" t="n">
         <v>27000</v>
       </c>
-      <c r="G11" s="19" t="n">
+      <c r="G11" s="20" t="n">
         <v>81000</v>
       </c>
-      <c r="H11" s="20" t="n">
+      <c r="H11" s="21" t="n">
         <v>554400</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="21" t="n">
         <v>345600</v>
       </c>
-      <c r="J11" s="20" t="n">
+      <c r="J11" s="21" t="n">
         <v>72000</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="21" t="n">
         <v>273600</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Coperate G</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="19" t="n">
         <v>8400000</v>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="19" t="n">
         <v>1050000</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>924000</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>126000</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="20" t="n">
         <v>31500</v>
       </c>
-      <c r="G12" s="19" t="n">
+      <c r="G12" s="20" t="n">
         <v>94500</v>
       </c>
-      <c r="H12" s="20" t="n">
+      <c r="H12" s="21" t="n">
         <v>646800</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="21" t="n">
         <v>403200</v>
       </c>
-      <c r="J12" s="20" t="n">
+      <c r="J12" s="21" t="n">
         <v>84000</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="21" t="n">
         <v>319200</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Coperate H</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="19" t="n">
         <v>9600000</v>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="19" t="n">
         <v>1200000</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="20" t="n">
         <v>1056000</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="20" t="n">
         <v>144000</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="20" t="n">
         <v>36000</v>
       </c>
-      <c r="G13" s="19" t="n">
+      <c r="G13" s="20" t="n">
         <v>108000</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H13" s="21" t="n">
         <v>739200</v>
       </c>
-      <c r="I13" s="20" t="n">
+      <c r="I13" s="21" t="n">
         <v>460800</v>
       </c>
-      <c r="J13" s="20" t="n">
+      <c r="J13" s="21" t="n">
         <v>96000</v>
       </c>
-      <c r="K13" s="20" t="n">
+      <c r="K13" s="21" t="n">
         <v>364800</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Coperate I</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n">
+      <c r="B14" s="19" t="n">
         <v>10800000</v>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>1350000</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="20" t="n">
         <v>1188000</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="20" t="n">
         <v>162000</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="20" t="n">
         <v>40500</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="20" t="n">
         <v>121500</v>
       </c>
-      <c r="H14" s="20" t="n">
+      <c r="H14" s="21" t="n">
         <v>831600</v>
       </c>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="21" t="n">
         <v>518400</v>
       </c>
-      <c r="J14" s="20" t="n">
+      <c r="J14" s="21" t="n">
         <v>108000</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="K14" s="21" t="n">
         <v>410400</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>Coperate J</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="19" t="n">
         <v>12000000</v>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>1500000</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="20" t="n">
         <v>1320000</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="20" t="n">
         <v>180000</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="20" t="n">
         <v>45000</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G15" s="20" t="n">
         <v>135000</v>
       </c>
-      <c r="H15" s="20" t="n">
+      <c r="H15" s="21" t="n">
         <v>924000</v>
       </c>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="21" t="n">
         <v>576000</v>
       </c>
-      <c r="J15" s="20" t="n">
+      <c r="J15" s="21" t="n">
         <v>120000</v>
       </c>
-      <c r="K15" s="20" t="n">
+      <c r="K15" s="21" t="n">
         <v>456000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="23" t="n">
         <v>66000000</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <v>8250000</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <v>7260000</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="23" t="n">
         <v>990000</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="23" t="n">
         <v>247500</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="23" t="n">
         <v>742500</v>
       </c>
-      <c r="H16" s="22" t="n">
+      <c r="H16" s="23" t="n">
         <v>5082000</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="23" t="n">
         <v>3168000</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="23" t="n">
         <v>660000</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="23" t="n">
         <v>2508000</v>
       </c>
     </row>
@@ -1964,214 +2040,214 @@
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
+      <c r="E4" s="6" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>รายการ</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Scenario A — Cost 0.11</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>หน่วย</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Scenario B — Cost 0.077</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>หน่วย</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>ราคาขาย/สลิป</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="13" t="n">
         <v>0.125</v>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>0.125</v>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ต้นทุน/สลิป</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="13" t="n">
         <v>0.11</v>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>0.077</v>
       </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>GP/สลิป</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="13" t="n">
         <v>0.015</v>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>0.048</v>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>GP %</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>0.384</v>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>เรทคอม (% revenue)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ค่าคอม/สลิป</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="13" t="n">
         <v>0.00375</v>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.01</v>
       </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Net GP/สลิป</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="13" t="n">
         <v>0.01125</v>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="24" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>0.038</v>
       </c>
-      <c r="E12" s="24" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Net margin %</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>0.09</v>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>0.304</v>
       </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="25" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2186,4 +2262,1002 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>THUNDER
+API</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>คู่มือการใช้งาน (USER GUIDE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>อธิบายความหมายของแต่ละช่อง · สูตรการคำนวณ · สมมติฐานที่ใช้</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>📁 ภาพรวมไฟล์ (มี 5 sheet)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ใช้ทำอะไร</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ใครเปิด</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>เห็น Scenario A vs B + เรทคอมแนะนำในหน้าเดียว</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>ผู้บริหาร / Sales Lead</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>1 Month</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>ตารางค่าคอมสำหรับสัญญารายเดือน (10 tier)</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>ทีมเซลส์ทำดีลรายเดือน</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>12 Month</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>ตารางค่าคอมสำหรับสัญญารายปี (Slips × 12)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>ทีมเซลส์ทำดีลรายปี</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Per-Slip Detail</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>ค่าคอม/สลิป ใช้ประมาณการ tier นอกตาราง</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>นัก quote ราคา ad-hoc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>คู่มือ</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>เอกสารนี้ — อธิบายทุกช่อง</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>ทีมใหม่ / Onboarding</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>🔧 สมมติฐานสำคัญ (Constants)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ค่าคงที่</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ค่า</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>ราคาขาย MOU</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>0.125 บ./สลิป (flat)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ลูกค้าจ่ายเท่ากันทุก tier ตามตาราง MOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario A</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>0.11 บ./สลิป</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>กรณีลูกค้าใช้ Other-source 100% (ราคา KBank Other ตาม MOU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario B</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>0.077 บ./สลิป</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>กรณี traffic mix blend ~30% K-src / 70% Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>เรทคอม A</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>3% ของ revenue</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>แนะนำเมื่อ margin บาง (Scenario A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>เรทคอม B</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>8% ของ revenue</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>แนะนำเมื่อ margin หนา (Scenario B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>📊 ชีต Summary — คำอธิบายช่อง</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>ช่อง</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>สูตร</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ความหมาย</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>ราคาขาย MOU</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>0.125 บ. (ค่าคงที่)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>ราคาที่ EasySlip คิดจากลูกค้า (บาท/สลิป) ตาม MOU เท่ากันทุก tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน/สลิป</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>0.11 หรือ 0.077</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>ต้นทุนที่ต้องจ่ายให้ KBank ผ่าน Thunder Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>GP/สลิป</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>ราคาขาย − ต้นทุน</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้นต่อสลิป ก่อนหักค่าคอม</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>GP %</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>GP ÷ ราคาขาย</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>อัตรากำไรขั้นต้น (% ของรายได้)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>เรทคอมแนะนำ</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>3% หรือ 8%</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>% ของ revenue ที่จ่ายให้เซลส์</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Net margin หลังคอม</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>(ราคาขาย − ต้นทุน − ค่าคอม) ÷ ราคาขาย</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>อัตรากำไรสุทธิหลังหักค่าคอม (ก่อนหัก opex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>📋 ชีต 1 Month / 12 Month — คำอธิบายช่อง</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>ช่อง</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>สูตร</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>ความหมาย / ตัวอย่าง (Coperate J)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>ระดับแพ็กเกจ MOU (Coperate A → J) ตามจำนวนสลิปที่ลูกค้าซื้อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Slips/period</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>base × ตัวคูณ (1 หรือ 12)</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>จำนวนสลิปทั้งหมดในรอบสัญญา · J = 1,000,000 (1mo) / 12,000,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Price/period</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Slips × 0.125</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>รายได้รวมที่ EasySlip รับ · J = 125,000 (1mo) / 1,500,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Cost (Scenario A)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Slips × 0.11</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>ต้นทุนรวมที่จ่าย KBank · J = 110,000 (1mo) / 1,320,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>GP (Scenario A)</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Price − Cost</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น · J = 15,000 (1mo) / 180,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Comm @3%</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Price × 0.03</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>ค่าคอมที่จ่ายเซลส์ · J = 3,750 (1mo) / 45,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Net GP (Scenario A)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>GP − Comm</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิที่บริษัทเก็บได้ · J = 11,250 (1mo) / 135,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Cost (Scenario B)</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Slips × 0.077</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>ต้นทุนกรณี mix blend · J = 77,000 (1mo) / 924,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>GP (Scenario B)</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Price − Cost</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น · J = 48,000 (1mo) / 576,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Comm @8%</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Price × 0.08</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>ค่าคอมที่จ่ายเซลส์ · J = 10,000 (1mo) / 120,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Net GP (Scenario B)</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>GP − Comm</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิ · J = 38,000 (1mo) / 456,000 (12mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>รวม (Total)</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>SUM(ทุกแพ็ก A–J)</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>ผลรวมทุก tier ใช้ดูเพดานยอดรวมถ้าขายได้ทั้งกระดาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>🔬 ชีต Per-Slip Detail — คำอธิบายช่อง</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>ช่อง</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>สูตร</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>ใช้ยังไง</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>ราคาขาย/สลิป</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>0.125 บ. (คงที่)</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>ใช้เป็นฐานคำนวณรายได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน/สลิป</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>0.11 หรือ 0.077</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>ดูตามที่ลูกค้า lock mix ใน MOU</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>GP/สลิป</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>ราคาขาย − ต้นทุน</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Margin ต่อสลิป ก่อนคอม</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>GP %</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>GP ÷ ราคาขาย</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>% margin ต่อสลิป</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>เรทคอม</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>3% หรือ 8%</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>% ของรายได้ที่จ่ายเซลส์</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>ค่าคอม/สลิป</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>ราคาขาย × เรท</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>ใช้คูณจำนวนสลิปคำนวณคอมจริง (เช่น 250,000 สลิป × 0.00375 = 937.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Net GP/สลิป</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>ราคาขาย − ต้นทุน − ค่าคอม</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Margin สุทธิต่อสลิป</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="28" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Net margin %</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Net GP ÷ ราคาขาย</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>% margin สุทธิหลังหักคอม</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>⚡ วิธีใช้งานเร็ว (Sales Playbook)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>ทำอะไร</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>ดูที่ Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>เช็คก่อน: ลูกค้า traffic เป็น K-src/Other เท่าไร — ถ้าไม่รู้ → ใช้ Scenario A safe</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>ถาม budget ลูกค้า → ดูว่าตรงกับ Coperate ตัวไหน</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>1 Month / 12 Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>อ่านช่อง Comm ของ Scenario ที่ใช้ → คือยอดที่เซลส์จะได้</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>1 Month / 12 Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>ดูช่อง Net GP → ดูว่าบริษัทเหลือกำไรเท่าไรหลังจ่ายเซลส์</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>1 Month / 12 Month</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="28" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>ถ้าใช้ Scenario B ต้องเขียนใน MOU: ลูกค้ารับประกัน K-src ≥ 30%</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>Summary (หัวข้อข้อระวัง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>ถ้า tier ลูกค้านอกตาราง (เช่น 250k สลิป) → ใช้ Per-Slip Detail คูณเอง</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Per-Slip Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ ข้อควรระวัง</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>รายละเอียด</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="n"/>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>ราคาขาย flat 0.125</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>ไม่ใช่ tier discount เหมือนแพ็กเกจมาตรฐาน — ทุกระดับจ่าย 0.125 บ./สลิปเท่ากัน ดังนั้นแพ็กใหญ่ไม่ได้กำไรเพิ่ม % ต่างจาก Web Pricing</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="n"/>
+    </row>
+    <row r="67" ht="42" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน 0.077 ไม่ใช่ค่ามาตรฐาน</t>
+        </is>
+      </c>
+      <c r="B67" s="18" t="inlineStr">
+        <is>
+          <t>เป็นค่าประมาณกรณี mix blend 30/70 ลูกค้าจริงต้องเช็ค traffic mix ก่อน — ถ้าใช้ Other เกิน 70% ต้นทุนทะลุ 0.077 ทันที</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="n"/>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Net GP ≠ Net Profit</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>Net GP ในไฟล์นี้ = หลังหักคอม แต่ยังไม่หัก opex (server, dev, support, sales operation) — ของจริงเหลือน้อยกว่านี้อีก 10–20%</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="n"/>
+    </row>
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>ตัวเลขในไฟล์เป็นราคา flat ตาม MOU (ราคาที่แสดงในตารางลูกค้า) ไม่ได้แยก excl/incl VAT — ถ้าจะใช้คำนวณงบจริง ปรึกษาบัญชี</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A64:C64"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
+++ b/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
@@ -11,7 +11,6 @@
     <sheet name="1 Month" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="12 Month" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Per-Slip Detail" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="คู่มือ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,6 +70,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009C5700"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="003F3F3F"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -229,6 +234,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -244,16 +252,13 @@
     <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -621,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -658,11 +663,31 @@
           <t>ราคาขายพื้นฐาน (THB)</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -732,11 +757,31 @@
           <t>เปรียบเทียบ Scenario ต้นทุน</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -820,11 +865,31 @@
           <t>หลักคิดเรทค่าคอม</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="6" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -837,10 +902,26 @@
           <t>margin บางมาก (12%) → ให้คอม 3% revenue บริษัทเหลือ ~9% รองรับ opex ได้</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -853,10 +934,26 @@
           <t>margin หนา (38.4%) → ให้คอม 8% revenue ได้ บริษัทเหลือ ~30% เซลส์ได้แรง</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="6" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -869,10 +966,26 @@
           <t>A @ 25% ของ GP ≈ 3% revenue · B @ 20% ของ GP ≈ 7.7% revenue</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="6" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -885,23 +998,501 @@
           <t>ถ้าใช้ Scenario B ต้อง lock traffic mix ใน MOU (เช่น K-src ≥ 30%)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="6" t="n"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>⚡ วิธีใช้งานเร็ว (Sales Playbook)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>ทำอะไร</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>เช็คก่อน: ลูกค้า traffic เป็น K-src/Other เท่าไร — ถ้าไม่รู้ → ใช้ Scenario A safe</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>ถาม budget ลูกค้า → ดูว่าตรงกับ Coperate ตัวไหน (เปิดแท็บ 1 Month หรือ 12 Month)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>อ่านช่อง Comm ของ Scenario ที่ใช้ → คือยอดที่เซลส์จะได้</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>ดูช่อง Net GP → ดูว่าบริษัทเหลือกำไรเท่าไรหลังจ่ายเซลส์</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>ถ้าใช้ Scenario B ต้องเขียนใน MOU: ลูกค้ารับประกัน K-src ≥ 30%</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>ถ้า tier ลูกค้านอกตาราง (เช่น 250k สลิป) → ใช้แท็บ Per-Slip Detail คูณเอง</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>⚠️ ข้อควรระวัง</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>หัวข้อ</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>รายละเอียด</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>ราคาขาย flat 0.125</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>ไม่ใช่ tier discount เหมือนแพ็กเกจมาตรฐาน — ทุกระดับจ่าย 0.125 บ./สลิปเท่ากัน ดังนั้นแพ็กใหญ่ไม่ได้กำไรเพิ่ม % ต่างจาก Web Pricing</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="42" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน 0.077 ไม่ใช่ค่ามาตรฐาน</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>เป็นค่าประมาณกรณี mix blend 30/70 ลูกค้าจริงต้องเช็ค traffic mix ก่อน — ถ้าใช้ Other เกิน 70% ต้นทุนทะลุ 0.077 ทันที</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Net GP ≠ Net Profit</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>Net GP ในไฟล์นี้ = หลังหักคอม แต่ยังไม่หัก opex (server, dev, support, sales operation) — ของจริงเหลือน้อยกว่านี้อีก 10–20%</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>ตัวเลขในไฟล์เป็นราคา flat ตาม MOU (ราคาที่แสดงในตารางลูกค้า) ไม่ได้แยก excl/incl VAT — ถ้าจะใช้คำนวณงบจริง ปรึกษาบัญชี</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A13:F13"/>
+  <mergeCells count="24">
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B21:F21"/>
     <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="B23:F23"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="C1:F1"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="C2:F2"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -913,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -955,24 +1546,56 @@
           <t>ดีลและราคา</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO A — ต้นทุน 0.11 บ./สลิป</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO B — ต้นทุน 0.077 บ./สลิป</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="6" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -1037,34 +1660,34 @@
           <t>Coperate A</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="20" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>12500</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>11000</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>1500</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>375</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>1125</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="22" t="n">
         <v>7700</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="22" t="n">
         <v>4800</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>1000</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>3800</v>
       </c>
     </row>
@@ -1074,34 +1697,34 @@
           <t>Coperate B</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="20" t="n">
         <v>200000</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>25000</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>22000</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>3000</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <v>750</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>2250</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="22" t="n">
         <v>15400</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>9600</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>2000</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>7600</v>
       </c>
     </row>
@@ -1111,34 +1734,34 @@
           <t>Coperate C</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="20" t="n">
         <v>300000</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>37500</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>33000</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>4500</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="21" t="n">
         <v>1125</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>3375</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="22" t="n">
         <v>23100</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>14400</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>3000</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>11400</v>
       </c>
     </row>
@@ -1148,34 +1771,34 @@
           <t>Coperate D</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="20" t="n">
         <v>400000</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <v>50000</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>44000</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>6000</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <v>1500</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>4500</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="22" t="n">
         <v>30800</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="22" t="n">
         <v>19200</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="22" t="n">
         <v>4000</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="K9" s="22" t="n">
         <v>15200</v>
       </c>
     </row>
@@ -1185,34 +1808,34 @@
           <t>Coperate E</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="20" t="n">
         <v>500000</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="20" t="n">
         <v>62500</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>55000</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>7500</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <v>1875</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <v>5625</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="22" t="n">
         <v>38500</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <v>24000</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="22" t="n">
         <v>5000</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="K10" s="22" t="n">
         <v>19000</v>
       </c>
     </row>
@@ -1222,34 +1845,34 @@
           <t>Coperate F</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="20" t="n">
         <v>600000</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <v>75000</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>66000</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>9000</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>2250</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>6750</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="22" t="n">
         <v>46200</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <v>28800</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <v>6000</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>22800</v>
       </c>
     </row>
@@ -1259,34 +1882,34 @@
           <t>Coperate G</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="20" t="n">
         <v>700000</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="20" t="n">
         <v>87500</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>77000</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>10500</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <v>2625</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <v>7875</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="22" t="n">
         <v>53900</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="22" t="n">
         <v>33600</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="22" t="n">
         <v>7000</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="K12" s="22" t="n">
         <v>26600</v>
       </c>
     </row>
@@ -1296,34 +1919,34 @@
           <t>Coperate H</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="20" t="n">
         <v>800000</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="20" t="n">
         <v>100000</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>88000</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>12000</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <v>3000</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <v>9000</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H13" s="22" t="n">
         <v>61600</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="22" t="n">
         <v>38400</v>
       </c>
-      <c r="J13" s="21" t="n">
+      <c r="J13" s="22" t="n">
         <v>8000</v>
       </c>
-      <c r="K13" s="21" t="n">
+      <c r="K13" s="22" t="n">
         <v>30400</v>
       </c>
     </row>
@@ -1333,34 +1956,34 @@
           <t>Coperate I</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="20" t="n">
         <v>900000</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="20" t="n">
         <v>112500</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>99000</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>13500</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <v>3375</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="21" t="n">
         <v>10125</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>69300</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>43200</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>9000</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>34200</v>
       </c>
     </row>
@@ -1370,81 +1993,1196 @@
           <t>Coperate J</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="20" t="n">
         <v>1000000</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="20" t="n">
         <v>125000</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="21" t="n">
         <v>110000</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <v>15000</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="21" t="n">
         <v>3750</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="21" t="n">
         <v>11250</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="22" t="n">
         <v>77000</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="22" t="n">
         <v>48000</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="22" t="n">
         <v>10000</v>
       </c>
-      <c r="K15" s="21" t="n">
+      <c r="K15" s="22" t="n">
         <v>38000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>5500000</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>687500</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>605000</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>82500</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <v>20625</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="24" t="n">
         <v>61875</v>
       </c>
-      <c r="H16" s="23" t="n">
+      <c r="H16" s="24" t="n">
         <v>423500</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="24" t="n">
         <v>264000</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="24" t="n">
         <v>55000</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="24" t="n">
         <v>209000</v>
       </c>
     </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>📖 คำอธิบายช่อง (Field Guide — 1 Month)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>ช่อง</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>สูตร</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ความหมาย</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>ระดับแพ็กเกจ MOU (Coperate A → J) ตามจำนวนสลิปที่ลูกค้าซื้อ</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Slips/1 Month</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>base × 1</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>จำนวนสลิปทั้งหมดในรอบสัญญา · J = 1,000,000</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Price/1 Month</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Slips × 0.125</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>รายได้รวมที่ EasySlip รับจากลูกค้า · J = 125,000 บ.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Cost (A)</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Slips × 0.11</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>ต้นทุนรวมที่จ่าย KBank (Scenario A) · J = 110,000 บ.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>GP (A)</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Price − Cost (A)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario A · J = 15,000 บ.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Comm @3%</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Price × 0.03</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>ค่าคอมเซลส์ Scenario A · J = 3,750 บ.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Net GP (A)</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>GP − Comm</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอม Scenario A · J = 11,250 บ.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Cost (B)</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Slips × 0.077</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario B (mix blend) · J = 77,000 บ.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>GP (B)</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Price − Cost (B)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario B · J = 48,000 บ.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Comm @8%</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Price × 0.08</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>ค่าคอมเซลส์ Scenario B · J = 10,000 บ.</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Net GP (B)</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>GP − Comm</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอม Scenario B · J = 38,000 บ.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>รวม (Total)</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>SUM(A–J)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>ผลรวมทุก tier ใช้ดูเพดานยอดรวมถ้าขายได้ครบทุกแพ็ก</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>💡 จุดที่ต้องสังเกตในตารางนี้</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Scenario A = ลูกค้าใช้ Other-source 100% (worst case) — margin บาง ค่าคอม 3%</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Scenario B = mix blend ~30/70 — margin หนา ค่าคอม 8%</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>ค่าใน Net GP คือกำไรหลังหักคอมแล้ว ยังไม่หัก opex บริษัท</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>ถ้าลูกค้าซื้อจำนวนสลิปนอกตาราง → เปิดแท็บ Per-Slip Detail คำนวณเอง</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="38">
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E27:K27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E25:K25"/>
+    <mergeCell ref="B36:K36"/>
     <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E21:K21"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E24:K24"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="H4:K4"/>
-    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E29:K29"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="E20:K20"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B34:K34"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1457,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1499,24 +3237,56 @@
           <t>ดีลและราคา</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO A — ต้นทุน 0.11 บ./สลิป</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>SCENARIO B — ต้นทุน 0.077 บ./สลิป</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="6" t="n"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -1581,34 +3351,34 @@
           <t>Coperate A</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="20" t="n">
         <v>1200000</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>150000</v>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D6" s="21" t="n">
         <v>132000</v>
       </c>
-      <c r="E6" s="20" t="n">
+      <c r="E6" s="21" t="n">
         <v>18000</v>
       </c>
-      <c r="F6" s="20" t="n">
+      <c r="F6" s="21" t="n">
         <v>4500</v>
       </c>
-      <c r="G6" s="20" t="n">
+      <c r="G6" s="21" t="n">
         <v>13500</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="22" t="n">
         <v>92400</v>
       </c>
-      <c r="I6" s="21" t="n">
+      <c r="I6" s="22" t="n">
         <v>57600</v>
       </c>
-      <c r="J6" s="21" t="n">
+      <c r="J6" s="22" t="n">
         <v>12000</v>
       </c>
-      <c r="K6" s="21" t="n">
+      <c r="K6" s="22" t="n">
         <v>45600</v>
       </c>
     </row>
@@ -1618,34 +3388,34 @@
           <t>Coperate B</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="20" t="n">
         <v>2400000</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="20" t="n">
         <v>300000</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>264000</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>36000</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="21" t="n">
         <v>9000</v>
       </c>
-      <c r="G7" s="20" t="n">
+      <c r="G7" s="21" t="n">
         <v>27000</v>
       </c>
-      <c r="H7" s="21" t="n">
+      <c r="H7" s="22" t="n">
         <v>184800</v>
       </c>
-      <c r="I7" s="21" t="n">
+      <c r="I7" s="22" t="n">
         <v>115200</v>
       </c>
-      <c r="J7" s="21" t="n">
+      <c r="J7" s="22" t="n">
         <v>24000</v>
       </c>
-      <c r="K7" s="21" t="n">
+      <c r="K7" s="22" t="n">
         <v>91200</v>
       </c>
     </row>
@@ -1655,34 +3425,34 @@
           <t>Coperate C</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="20" t="n">
         <v>3600000</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>450000</v>
       </c>
-      <c r="D8" s="20" t="n">
+      <c r="D8" s="21" t="n">
         <v>396000</v>
       </c>
-      <c r="E8" s="20" t="n">
+      <c r="E8" s="21" t="n">
         <v>54000</v>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="21" t="n">
         <v>13500</v>
       </c>
-      <c r="G8" s="20" t="n">
+      <c r="G8" s="21" t="n">
         <v>40500</v>
       </c>
-      <c r="H8" s="21" t="n">
+      <c r="H8" s="22" t="n">
         <v>277200</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="22" t="n">
         <v>172800</v>
       </c>
-      <c r="J8" s="21" t="n">
+      <c r="J8" s="22" t="n">
         <v>36000</v>
       </c>
-      <c r="K8" s="21" t="n">
+      <c r="K8" s="22" t="n">
         <v>136800</v>
       </c>
     </row>
@@ -1692,34 +3462,34 @@
           <t>Coperate D</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="20" t="n">
         <v>4800000</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <v>600000</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="21" t="n">
         <v>528000</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="21" t="n">
         <v>72000</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="21" t="n">
         <v>18000</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="21" t="n">
         <v>54000</v>
       </c>
-      <c r="H9" s="21" t="n">
+      <c r="H9" s="22" t="n">
         <v>369600</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="22" t="n">
         <v>230400</v>
       </c>
-      <c r="J9" s="21" t="n">
+      <c r="J9" s="22" t="n">
         <v>48000</v>
       </c>
-      <c r="K9" s="21" t="n">
+      <c r="K9" s="22" t="n">
         <v>182400</v>
       </c>
     </row>
@@ -1729,34 +3499,34 @@
           <t>Coperate E</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="20" t="n">
         <v>6000000</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="20" t="n">
         <v>750000</v>
       </c>
-      <c r="D10" s="20" t="n">
+      <c r="D10" s="21" t="n">
         <v>660000</v>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E10" s="21" t="n">
         <v>90000</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="21" t="n">
         <v>22500</v>
       </c>
-      <c r="G10" s="20" t="n">
+      <c r="G10" s="21" t="n">
         <v>67500</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="22" t="n">
         <v>462000</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="22" t="n">
         <v>288000</v>
       </c>
-      <c r="J10" s="21" t="n">
+      <c r="J10" s="22" t="n">
         <v>60000</v>
       </c>
-      <c r="K10" s="21" t="n">
+      <c r="K10" s="22" t="n">
         <v>228000</v>
       </c>
     </row>
@@ -1766,34 +3536,34 @@
           <t>Coperate F</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="20" t="n">
         <v>7200000</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <v>900000</v>
       </c>
-      <c r="D11" s="20" t="n">
+      <c r="D11" s="21" t="n">
         <v>792000</v>
       </c>
-      <c r="E11" s="20" t="n">
+      <c r="E11" s="21" t="n">
         <v>108000</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="21" t="n">
         <v>27000</v>
       </c>
-      <c r="G11" s="20" t="n">
+      <c r="G11" s="21" t="n">
         <v>81000</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="22" t="n">
         <v>554400</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="22" t="n">
         <v>345600</v>
       </c>
-      <c r="J11" s="21" t="n">
+      <c r="J11" s="22" t="n">
         <v>72000</v>
       </c>
-      <c r="K11" s="21" t="n">
+      <c r="K11" s="22" t="n">
         <v>273600</v>
       </c>
     </row>
@@ -1803,34 +3573,34 @@
           <t>Coperate G</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="20" t="n">
         <v>8400000</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="20" t="n">
         <v>1050000</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="21" t="n">
         <v>924000</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="21" t="n">
         <v>126000</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="21" t="n">
         <v>31500</v>
       </c>
-      <c r="G12" s="20" t="n">
+      <c r="G12" s="21" t="n">
         <v>94500</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="22" t="n">
         <v>646800</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="22" t="n">
         <v>403200</v>
       </c>
-      <c r="J12" s="21" t="n">
+      <c r="J12" s="22" t="n">
         <v>84000</v>
       </c>
-      <c r="K12" s="21" t="n">
+      <c r="K12" s="22" t="n">
         <v>319200</v>
       </c>
     </row>
@@ -1840,34 +3610,34 @@
           <t>Coperate H</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
+      <c r="B13" s="20" t="n">
         <v>9600000</v>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="20" t="n">
         <v>1200000</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="21" t="n">
         <v>1056000</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="21" t="n">
         <v>144000</v>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F13" s="21" t="n">
         <v>36000</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G13" s="21" t="n">
         <v>108000</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H13" s="22" t="n">
         <v>739200</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="22" t="n">
         <v>460800</v>
       </c>
-      <c r="J13" s="21" t="n">
+      <c r="J13" s="22" t="n">
         <v>96000</v>
       </c>
-      <c r="K13" s="21" t="n">
+      <c r="K13" s="22" t="n">
         <v>364800</v>
       </c>
     </row>
@@ -1877,34 +3647,34 @@
           <t>Coperate I</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="20" t="n">
         <v>10800000</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="20" t="n">
         <v>1350000</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>1188000</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>162000</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="21" t="n">
         <v>40500</v>
       </c>
-      <c r="G14" s="20" t="n">
+      <c r="G14" s="21" t="n">
         <v>121500</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>831600</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="22" t="n">
         <v>518400</v>
       </c>
-      <c r="J14" s="21" t="n">
+      <c r="J14" s="22" t="n">
         <v>108000</v>
       </c>
-      <c r="K14" s="21" t="n">
+      <c r="K14" s="22" t="n">
         <v>410400</v>
       </c>
     </row>
@@ -1914,81 +3684,1196 @@
           <t>Coperate J</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="20" t="n">
         <v>12000000</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="20" t="n">
         <v>1500000</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="21" t="n">
         <v>1320000</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <v>180000</v>
       </c>
-      <c r="F15" s="20" t="n">
+      <c r="F15" s="21" t="n">
         <v>45000</v>
       </c>
-      <c r="G15" s="20" t="n">
+      <c r="G15" s="21" t="n">
         <v>135000</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="22" t="n">
         <v>924000</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="22" t="n">
         <v>576000</v>
       </c>
-      <c r="J15" s="21" t="n">
+      <c r="J15" s="22" t="n">
         <v>120000</v>
       </c>
-      <c r="K15" s="21" t="n">
+      <c r="K15" s="22" t="n">
         <v>456000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>รวม</t>
         </is>
       </c>
-      <c r="B16" s="23" t="n">
+      <c r="B16" s="24" t="n">
         <v>66000000</v>
       </c>
-      <c r="C16" s="23" t="n">
+      <c r="C16" s="24" t="n">
         <v>8250000</v>
       </c>
-      <c r="D16" s="23" t="n">
+      <c r="D16" s="24" t="n">
         <v>7260000</v>
       </c>
-      <c r="E16" s="23" t="n">
+      <c r="E16" s="24" t="n">
         <v>990000</v>
       </c>
-      <c r="F16" s="23" t="n">
+      <c r="F16" s="24" t="n">
         <v>247500</v>
       </c>
-      <c r="G16" s="23" t="n">
+      <c r="G16" s="24" t="n">
         <v>742500</v>
       </c>
-      <c r="H16" s="23" t="n">
+      <c r="H16" s="24" t="n">
         <v>5082000</v>
       </c>
-      <c r="I16" s="23" t="n">
+      <c r="I16" s="24" t="n">
         <v>3168000</v>
       </c>
-      <c r="J16" s="23" t="n">
+      <c r="J16" s="24" t="n">
         <v>660000</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="24" t="n">
         <v>2508000</v>
       </c>
     </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>📖 คำอธิบายช่อง (Field Guide — 12 Month)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>ช่อง</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>สูตร</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>ความหมาย</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>ระดับแพ็กเกจ MOU (Coperate A → J) ตามจำนวนสลิปที่ลูกค้าซื้อ</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Slips/12 Month</t>
+        </is>
+      </c>
+      <c r="B21" s="18" t="inlineStr">
+        <is>
+          <t>base × 12</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>จำนวนสลิปทั้งหมดในรอบสัญญา · J = 12,000,000</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Price/12 Month</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Slips × 0.125</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>รายได้รวมที่ EasySlip รับจากลูกค้า · J = 1,500,000 บ.</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Cost (A)</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>Slips × 0.11</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>ต้นทุนรวมที่จ่าย KBank (Scenario A) · J = 1,320,000 บ.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>GP (A)</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>Price − Cost (A)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario A · J = 180,000 บ.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Comm @3%</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Price × 0.03</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>ค่าคอมเซลส์ Scenario A · J = 45,000 บ.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Net GP (A)</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>GP − Comm</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอม Scenario A · J = 135,000 บ.</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Cost (B)</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>Slips × 0.077</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario B (mix blend) · J = 924,000 บ.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>GP (B)</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Price − Cost (B)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario B · J = 576,000 บ.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Comm @8%</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>Price × 0.08</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="inlineStr">
+        <is>
+          <t>ค่าคอมเซลส์ Scenario B · J = 120,000 บ.</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Net GP (B)</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>GP − Comm</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอม Scenario B · J = 456,000 บ.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>รวม (Total)</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>SUM(A–J)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="inlineStr">
+        <is>
+          <t>ผลรวมทุก tier ใช้ดูเพดานยอดรวมถ้าขายได้ครบทุกแพ็ก</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>💡 จุดที่ต้องสังเกตในตารางนี้</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Scenario A = ลูกค้าใช้ Other-source 100% (worst case) — margin บาง ค่าคอม 3%</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>Scenario B = mix blend ~30/70 — margin หนา ค่าคอม 8%</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>ค่าใน Net GP คือกำไรหลังหักคอมแล้ว ยังไม่หัก opex บริษัท</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>ถ้าลูกค้าซื้อจำนวนสลิปนอกตาราง → เปิดแท็บ Per-Slip Detail คำนวณเอง</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="38">
+    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="E26:K26"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E27:K27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E25:K25"/>
+    <mergeCell ref="B36:K36"/>
     <mergeCell ref="C2:K2"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E22:K22"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E21:K21"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E24:K24"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="H4:K4"/>
-    <mergeCell ref="C1:K1"/>
+    <mergeCell ref="E23:K23"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E29:K29"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="E20:K20"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E19:K19"/>
+    <mergeCell ref="E28:K28"/>
+    <mergeCell ref="E31:K31"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B37:K37"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B34:K34"/>
     <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2001,7 +4886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2037,10 +4922,26 @@
           <t>ค่าคอม / สลิป — ทั้งสอง Scenario</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -2078,7 +4979,7 @@
       <c r="B6" s="13" t="n">
         <v>0.125</v>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2086,7 +4987,7 @@
       <c r="D6" s="16" t="n">
         <v>0.125</v>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2101,7 +5002,7 @@
       <c r="B7" s="13" t="n">
         <v>0.11</v>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2109,7 +5010,7 @@
       <c r="D7" s="16" t="n">
         <v>0.077</v>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2124,7 +5025,7 @@
       <c r="B8" s="13" t="n">
         <v>0.015</v>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2132,7 +5033,7 @@
       <c r="D8" s="16" t="n">
         <v>0.048</v>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2147,7 +5048,7 @@
       <c r="B9" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2155,7 +5056,7 @@
       <c r="D9" s="17" t="n">
         <v>0.384</v>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2170,7 +5071,7 @@
       <c r="B10" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2178,7 +5079,7 @@
       <c r="D10" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="27" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2193,7 +5094,7 @@
       <c r="B11" s="13" t="n">
         <v>0.00375</v>
       </c>
-      <c r="C11" s="24" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2201,7 +5102,7 @@
       <c r="D11" s="16" t="n">
         <v>0.01</v>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2216,7 +5117,7 @@
       <c r="B12" s="13" t="n">
         <v>0.01125</v>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2224,7 +5125,7 @@
       <c r="D12" s="16" t="n">
         <v>0.038</v>
       </c>
-      <c r="E12" s="25" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
@@ -2239,7 +5140,7 @@
       <c r="B13" s="14" t="n">
         <v>0.09</v>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -2247,1016 +5148,158 @@
       <c r="D13" s="17" t="n">
         <v>0.304</v>
       </c>
-      <c r="E13" s="25" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>📖 วิธีใช้แท็บนี้</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="38" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>เมื่อไรใช้</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>ลูกค้าซื้อจำนวนสลิปที่ไม่ตรงตาราง 1 Month / 12 Month (เช่น 250,000 สลิป) ใช้ค่าใน "ค่าคอม/สลิป" คูณกับจำนวนสลิปที่ขายได้</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>ตัวอย่าง Scenario A</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>ลูกค้าซื้อ 250,000 สลิป → ค่าคอม = 250,000 × 0.00375 = 937.50 บ. · บริษัทเหลือ Net GP = 250,000 × 0.011 = 2,750 บ.</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>ตัวอย่าง Scenario B</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>ลูกค้าซื้อ 250,000 สลิป → ค่าคอม = 250,000 × 0.01 = 2,500 บ. · บริษัทเหลือ Net GP = 250,000 × 0.038 = 9,500 บ.</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>เลือก Scenario ยังไง</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>ถ้าไม่รู้ traffic mix → ใช้ A เพื่อ safe · ถ้า lock mix K-src ≥ 30% ใน MOU → ใช้ B</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="9">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="C2:E2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C69"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>THUNDER
-API</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>คู่มือการใช้งาน (USER GUIDE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>อธิบายความหมายของแต่ละช่อง · สูตรการคำนวณ · สมมติฐานที่ใช้</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>📁 ภาพรวมไฟล์ (มี 5 sheet)</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="6" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>ใช้ทำอะไร</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>ใครเปิด</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>เห็น Scenario A vs B + เรทคอมแนะนำในหน้าเดียว</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>ผู้บริหาร / Sales Lead</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>1 Month</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>ตารางค่าคอมสำหรับสัญญารายเดือน (10 tier)</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>ทีมเซลส์ทำดีลรายเดือน</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>12 Month</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>ตารางค่าคอมสำหรับสัญญารายปี (Slips × 12)</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>ทีมเซลส์ทำดีลรายปี</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Per-Slip Detail</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>ค่าคอม/สลิป ใช้ประมาณการ tier นอกตาราง</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>นัก quote ราคา ad-hoc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>คู่มือ</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>เอกสารนี้ — อธิบายทุกช่อง</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>ทีมใหม่ / Onboarding</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>🔧 สมมติฐานสำคัญ (Constants)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>ค่าคงที่</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>ค่า</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>หมายเหตุ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>ราคาขาย MOU</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>0.125 บ./สลิป (flat)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>ลูกค้าจ่ายเท่ากันทุก tier ตามตาราง MOU</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>ต้นทุน Scenario A</t>
-        </is>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>0.11 บ./สลิป</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>กรณีลูกค้าใช้ Other-source 100% (ราคา KBank Other ตาม MOU)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>ต้นทุน Scenario B</t>
-        </is>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>0.077 บ./สลิป</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>กรณี traffic mix blend ~30% K-src / 70% Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>เรทคอม A</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>3% ของ revenue</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>แนะนำเมื่อ margin บาง (Scenario A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>เรทคอม B</t>
-        </is>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>8% ของ revenue</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>แนะนำเมื่อ margin หนา (Scenario B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>📊 ชีต Summary — คำอธิบายช่อง</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>ช่อง</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>สูตร</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>ความหมาย</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>ราคาขาย MOU</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>0.125 บ. (ค่าคงที่)</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>ราคาที่ EasySlip คิดจากลูกค้า (บาท/สลิป) ตาม MOU เท่ากันทุก tier</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>ต้นทุน/สลิป</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>0.11 หรือ 0.077</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>ต้นทุนที่ต้องจ่ายให้ KBank ผ่าน Thunder Group</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>GP/สลิป</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>ราคาขาย − ต้นทุน</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้นต่อสลิป ก่อนหักค่าคอม</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>GP %</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t>GP ÷ ราคาขาย</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>อัตรากำไรขั้นต้น (% ของรายได้)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>เรทคอมแนะนำ</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
-        <is>
-          <t>3% หรือ 8%</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>% ของ revenue ที่จ่ายให้เซลส์</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Net margin หลังคอม</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>(ราคาขาย − ต้นทุน − ค่าคอม) ÷ ราคาขาย</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>อัตรากำไรสุทธิหลังหักค่าคอม (ก่อนหัก opex)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>📋 ชีต 1 Month / 12 Month — คำอธิบายช่อง</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="6" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>ช่อง</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>สูตร</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>ความหมาย / ตัวอย่าง (Coperate J)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>ระดับแพ็กเกจ MOU (Coperate A → J) ตามจำนวนสลิปที่ลูกค้าซื้อ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>Slips/period</t>
-        </is>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>base × ตัวคูณ (1 หรือ 12)</t>
-        </is>
-      </c>
-      <c r="C32" s="10" t="inlineStr">
-        <is>
-          <t>จำนวนสลิปทั้งหมดในรอบสัญญา · J = 1,000,000 (1mo) / 12,000,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Price/period</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>Slips × 0.125</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>รายได้รวมที่ EasySlip รับ · J = 125,000 (1mo) / 1,500,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>Cost (Scenario A)</t>
-        </is>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
-        <is>
-          <t>Slips × 0.11</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>ต้นทุนรวมที่จ่าย KBank · J = 110,000 (1mo) / 1,320,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>GP (Scenario A)</t>
-        </is>
-      </c>
-      <c r="B35" s="10" t="inlineStr">
-        <is>
-          <t>Price − Cost</t>
-        </is>
-      </c>
-      <c r="C35" s="10" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น · J = 15,000 (1mo) / 180,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Comm @3%</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>Price × 0.03</t>
-        </is>
-      </c>
-      <c r="C36" s="10" t="inlineStr">
-        <is>
-          <t>ค่าคอมที่จ่ายเซลส์ · J = 3,750 (1mo) / 45,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Net GP (Scenario A)</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="inlineStr">
-        <is>
-          <t>GP − Comm</t>
-        </is>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>กำไรสุทธิที่บริษัทเก็บได้ · J = 11,250 (1mo) / 135,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>Cost (Scenario B)</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>Slips × 0.077</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>ต้นทุนกรณี mix blend · J = 77,000 (1mo) / 924,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>GP (Scenario B)</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>Price − Cost</t>
-        </is>
-      </c>
-      <c r="C39" s="10" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น · J = 48,000 (1mo) / 576,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>Comm @8%</t>
-        </is>
-      </c>
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>Price × 0.08</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="inlineStr">
-        <is>
-          <t>ค่าคอมที่จ่ายเซลส์ · J = 10,000 (1mo) / 120,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Net GP (Scenario B)</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="inlineStr">
-        <is>
-          <t>GP − Comm</t>
-        </is>
-      </c>
-      <c r="C41" s="10" t="inlineStr">
-        <is>
-          <t>กำไรสุทธิ · J = 38,000 (1mo) / 456,000 (12mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>รวม (Total)</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
-        <is>
-          <t>SUM(ทุกแพ็ก A–J)</t>
-        </is>
-      </c>
-      <c r="C42" s="10" t="inlineStr">
-        <is>
-          <t>ผลรวมทุก tier ใช้ดูเพดานยอดรวมถ้าขายได้ทั้งกระดาน</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>🔬 ชีต Per-Slip Detail — คำอธิบายช่อง</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="6" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>ช่อง</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>สูตร</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>ใช้ยังไง</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>ราคาขาย/สลิป</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="inlineStr">
-        <is>
-          <t>0.125 บ. (คงที่)</t>
-        </is>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>ใช้เป็นฐานคำนวณรายได้</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>ต้นทุน/สลิป</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
-        <is>
-          <t>0.11 หรือ 0.077</t>
-        </is>
-      </c>
-      <c r="C47" s="10" t="inlineStr">
-        <is>
-          <t>ดูตามที่ลูกค้า lock mix ใน MOU</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>GP/สลิป</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>ราคาขาย − ต้นทุน</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>Margin ต่อสลิป ก่อนคอม</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>GP %</t>
-        </is>
-      </c>
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>GP ÷ ราคาขาย</t>
-        </is>
-      </c>
-      <c r="C49" s="10" t="inlineStr">
-        <is>
-          <t>% margin ต่อสลิป</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>เรทคอม</t>
-        </is>
-      </c>
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>3% หรือ 8%</t>
-        </is>
-      </c>
-      <c r="C50" s="10" t="inlineStr">
-        <is>
-          <t>% ของรายได้ที่จ่ายเซลส์</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>ค่าคอม/สลิป</t>
-        </is>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>ราคาขาย × เรท</t>
-        </is>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>ใช้คูณจำนวนสลิปคำนวณคอมจริง (เช่น 250,000 สลิป × 0.00375 = 937.5)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Net GP/สลิป</t>
-        </is>
-      </c>
-      <c r="B52" s="10" t="inlineStr">
-        <is>
-          <t>ราคาขาย − ต้นทุน − ค่าคอม</t>
-        </is>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
-        <is>
-          <t>Margin สุทธิต่อสลิป</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Net margin %</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>Net GP ÷ ราคาขาย</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>% margin สุทธิหลังหักคอม</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>⚡ วิธีใช้งานเร็ว (Sales Playbook)</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="6" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Step</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>ทำอะไร</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr">
-        <is>
-          <t>ดูที่ Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>เช็คก่อน: ลูกค้า traffic เป็น K-src/Other เท่าไร — ถ้าไม่รู้ → ใช้ Scenario A safe</t>
-        </is>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="28" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>ถาม budget ลูกค้า → ดูว่าตรงกับ Coperate ตัวไหน</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>1 Month / 12 Month</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B59" s="10" t="inlineStr">
-        <is>
-          <t>อ่านช่อง Comm ของ Scenario ที่ใช้ → คือยอดที่เซลส์จะได้</t>
-        </is>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
-        <is>
-          <t>1 Month / 12 Month</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="inlineStr">
-        <is>
-          <t>ดูช่อง Net GP → ดูว่าบริษัทเหลือกำไรเท่าไรหลังจ่ายเซลส์</t>
-        </is>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>1 Month / 12 Month</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="inlineStr">
-        <is>
-          <t>ถ้าใช้ Scenario B ต้องเขียนใน MOU: ลูกค้ารับประกัน K-src ≥ 30%</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>Summary (หัวข้อข้อระวัง)</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>ถ้า tier ลูกค้านอกตาราง (เช่น 250k สลิป) → ใช้ Per-Slip Detail คูณเอง</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Per-Slip Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
-        <is>
-          <t>⚠️ ข้อควรระวัง</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="6" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>หัวข้อ</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>รายละเอียด</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="n"/>
-    </row>
-    <row r="66" ht="42" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
-        <is>
-          <t>ราคาขาย flat 0.125</t>
-        </is>
-      </c>
-      <c r="B66" s="18" t="inlineStr">
-        <is>
-          <t>ไม่ใช่ tier discount เหมือนแพ็กเกจมาตรฐาน — ทุกระดับจ่าย 0.125 บ./สลิปเท่ากัน ดังนั้นแพ็กใหญ่ไม่ได้กำไรเพิ่ม % ต่างจาก Web Pricing</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="n"/>
-    </row>
-    <row r="67" ht="42" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
-        <is>
-          <t>ต้นทุน 0.077 ไม่ใช่ค่ามาตรฐาน</t>
-        </is>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>เป็นค่าประมาณกรณี mix blend 30/70 ลูกค้าจริงต้องเช็ค traffic mix ก่อน — ถ้าใช้ Other เกิน 70% ต้นทุนทะลุ 0.077 ทันที</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="n"/>
-    </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
-        <is>
-          <t>Net GP ≠ Net Profit</t>
-        </is>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>Net GP ในไฟล์นี้ = หลังหักคอม แต่ยังไม่หัก opex (server, dev, support, sales operation) — ของจริงเหลือน้อยกว่านี้อีก 10–20%</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="n"/>
-    </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>VAT</t>
-        </is>
-      </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>ตัวเลขในไฟล์เป็นราคา flat ตาม MOU (ราคาที่แสดงในตารางลูกค้า) ไม่ได้แยก excl/incl VAT — ถ้าจะใช้คำนวณงบจริง ปรึกษาบัญชี</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A64:C64"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
+++ b/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
@@ -79,7 +79,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +94,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -204,22 +209,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,8 +230,14 @@
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -240,25 +245,25 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -626,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -653,51 +658,52 @@
     <row r="2" ht="22" customHeight="1">
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ค่าคอมทีมเซลส์ · ขาย MOU แบบเลือกจำนวนสลิปได้ · บริษัท อีซี่สลิป จำกัด</t>
-        </is>
-      </c>
-    </row>
+          <t>ค่าคอมมิชชันทีมขาย · ขาย MOU แบบเลือกจำนวนสลิปได้ · บริษัท อีซี่สลิป จำกัด</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>ราคาขายพื้นฐาน (THB)</t>
+          <t>🎛️ ตั้งค่าหลัก — แก้ไขตัวเลขในช่องเหลืองได้เลย (สูตรทั้งไฟล์จะอัปเดตอัตโนมัติ)</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>รายการ</t>
+          <t>ค่าตั้งต้น</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>ราคา/สลิป</t>
+          <t>ค่า</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -707,24 +713,24 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>ราคาขาย MOU (flat ทุก tier)</t>
+          <t>ราคาขาย MOU</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
@@ -732,769 +738,912 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>บาท/สลิป</t>
+          <t>บ./สลิป</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>เปรียบเทียบ Scenario ต้นทุน</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+          <t>ราคาคงที่ทุก tier ตามตาราง MOU</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario A</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>บ./สลิป</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>แหล่ง Other-source 100% (ราคา KBank คงที่)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario B</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>บ./สลิป</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>ส่วนผสม ~30% K-src / 70% Other</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>อัตราค่าคอมมิชชัน Scenario A</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>% ของรายได้ที่จ่ายให้เซลส์ (ใช้กับ Scenario A)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>อัตราค่าคอมมิชชัน Scenario B</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>% ของรายได้ที่จ่ายให้เซลส์ (ใช้กับ Scenario B)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>เปรียบเทียบ Scenario ต้นทุน (อ้างอิงจากค่า Settings ด้านบน)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>ต้นทุน/สลิป</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>GP/สลิป</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>GP %</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>เรทคอมแนะนำ</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Net margin หลังคอม</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>A — Other-source 100%</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>B — Mix blend (~30/70)</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>0.304</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>หลักคิดเรทค่าคอม</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Scenario A (cost 0.11)</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>margin บางมาก (12%) → ให้คอม 3% revenue บริษัทเหลือ ~9% รองรับ opex ได้</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Scenario B (cost 0.077)</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>margin หนา (38.4%) → ให้คอม 8% revenue ได้ บริษัทเหลือ ~30% เซลส์ได้แรง</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>ทางเลือก: คิดเป็น % ของ GP</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A @ 25% ของ GP ≈ 3% revenue · B @ 20% ของ GP ≈ 7.7% revenue</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>A — แหล่ง Other-source 100%</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="C14" s="14">
+        <f>Summary!$B$6-Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>(Summary!$B$6-Summary!$B$7)/Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>(Summary!$B$6-Summary!$B$7-Summary!$B$6*Summary!$B$9)/Summary!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>B — ส่วนผสม (~30/70)</t>
+        </is>
+      </c>
+      <c r="B15" s="17">
+        <f>Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>Summary!$B$6-Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="D15" s="18">
+        <f>(Summary!$B$6-Summary!$B$8)/Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="F15" s="18">
+        <f>(Summary!$B$6-Summary!$B$8-Summary!$B$6*Summary!$B$10)/Summary!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>แนวคิดอัตราค่าคอมมิชชัน</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Scenario A (ต้นทุน 0.11)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>อัตรากำไรบาง (12%) → ให้ค่าคอม 3% ของรายได้ บริษัทเหลือ ~9% รองรับค่าใช้จ่าย</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Scenario B (ต้นทุน 0.077)</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>อัตรากำไรหนา (38.4%) → ให้ค่าคอม 8% ของรายได้ บริษัทเหลือ ~30% เซลส์ได้ผลตอบแทนดี</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>ทางเลือก: คิดเป็น % ของกำไรขั้นต้น</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>A @ 25% ของกำไรขั้นต้น ≈ 3% ของรายได้ · B @ 20% ของกำไรขั้นต้น ≈ 7.7% ของรายได้</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>ข้อระวัง MOU</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>ถ้าใช้ Scenario B ต้อง lock traffic mix ใน MOU (เช่น K-src ≥ 30%)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>⚡ วิธีใช้งานเร็ว (Sales Playbook)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>⚡ วิธีใช้งานอย่างรวดเร็ว (Sales Playbook)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>ทำอะไร</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>เช็คก่อน: ลูกค้า traffic เป็น K-src/Other เท่าไร — ถ้าไม่รู้ → ใช้ Scenario A safe</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>ถาม budget ลูกค้า → ดูว่าตรงกับ Coperate ตัวไหน (เปิดแท็บ 1 Month หรือ 12 Month)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>อ่านช่อง Comm ของ Scenario ที่ใช้ → คือยอดที่เซลส์จะได้</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>ดูช่อง Net GP → ดูว่าบริษัทเหลือกำไรเท่าไรหลังจ่ายเซลส์</t>
-        </is>
-      </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>ถ้าใช้ Scenario B ต้องเขียนใน MOU: ลูกค้ารับประกัน K-src ≥ 30%</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบก่อน: ลูกค้ามี traffic เป็น K-src/Other เท่าไร — ถ้าไม่ทราบ → ใช้ Scenario A เพื่อความปลอดภัย</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="19" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>สอบถามงบประมาณของลูกค้า → ตรวจสอบว่าตรงกับ Coperate ตัวไหน (เปิดแท็บ 1 เดือน หรือ 12 เดือน)</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>อ่านช่อง Comm ของ Scenario ที่ใช้ → คือยอดที่เซลส์จะได้รับ</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>ตรวจสอบช่อง Net GP → ดูว่าบริษัทเหลือกำไรเท่าไรหลังจ่ายค่าคอมมิชชัน</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>ถ้าใช้ Scenario B ต้องเขียนใน MOU: ลูกค้ารับประกัน K-src ≥ 30%</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>ถ้า tier ลูกค้านอกตาราง (เช่น 250k สลิป) → ใช้แท็บ Per-Slip Detail คูณเอง</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>ถ้า tier ของลูกค้าไม่อยู่ในตาราง (เช่น 250,000 สลิป) → ใช้แท็บ Per-Slip Detail คูณเอง</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>⚠️ ข้อควรระวัง</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>หัวข้อ</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>รายละเอียด</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="42" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>ราคาขาย flat 0.125</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>ไม่ใช่ tier discount เหมือนแพ็กเกจมาตรฐาน — ทุกระดับจ่าย 0.125 บ./สลิปเท่ากัน ดังนั้นแพ็กใหญ่ไม่ได้กำไรเพิ่ม % ต่างจาก Web Pricing</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="42" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>ราคาขายคงที่ 0.125</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>ไม่ใช่ส่วนลดตาม tier เหมือนแพ็กเกจมาตรฐาน — ทุกระดับจ่าย 0.125 บาท/สลิปเท่ากัน ดังนั้นแพ็กใหญ่จึงไม่ได้กำไรเพิ่ม % ต่างจาก Web Pricing</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="42" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>ต้นทุน 0.077 ไม่ใช่ค่ามาตรฐาน</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>เป็นค่าประมาณกรณี mix blend 30/70 ลูกค้าจริงต้องเช็ค traffic mix ก่อน — ถ้าใช้ Other เกิน 70% ต้นทุนทะลุ 0.077 ทันที</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>เป็นค่าประมาณกรณีส่วนผสม 30/70 ลูกค้าจริงต้องตรวจสอบ traffic mix ก่อน — ถ้าใช้ Other เกิน 70% ต้นทุนจะเกิน 0.077 ทันที</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Net GP ≠ Net Profit</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>Net GP ในไฟล์นี้ = หลังหักคอม แต่ยังไม่หัก opex (server, dev, support, sales operation) — ของจริงเหลือน้อยกว่านี้อีก 10–20%</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Net GP ในไฟล์นี้ = หลังหักค่าคอมมิชชันแล้ว แต่ยังไม่หักค่าใช้จ่าย (server, dev, support, sales operation) — ของจริงเหลือน้อยกว่านี้อีก 10–20%</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>ตัวเลขในไฟล์เป็นราคา flat ตาม MOU (ราคาที่แสดงในตารางลูกค้า) ไม่ได้แยก excl/incl VAT — ถ้าจะใช้คำนวณงบจริง ปรึกษาบัญชี</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>ตัวเลขในไฟล์เป็นราคาคงที่ตาม MOU (ราคาที่แสดงในตารางลูกค้า) ไม่ได้แยก excl/incl VAT — ถ้าจะใช้คำนวณงบจริง ปรึกษาฝ่ายบัญชี</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t> </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B16:F16"/>
+  <mergeCells count="30">
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
     <mergeCell ref="B21:F21"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="D8:F8"/>
     <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="D10:F10"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B15:F15"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="C2:F2"/>
+    <mergeCell ref="D6:F6"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:ZZ1000" calculatedColumn="1" emptyCellReference="1" evalError="1" formula="1" formulaRange="1" listDataValidation="1" numberStoredAsText="1" twoDigitTextYear="1" unlockedFormula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1536,10 +1685,11 @@
     <row r="2" ht="22" customHeight="1">
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ราคาขาย flat 0.125 บ./สลิป · ตัวเลขเป็นบาททั้งหมด · multiplier = 1 เดือน</t>
-        </is>
-      </c>
-    </row>
+          <t>ตัวเลขทั้งหมดคำนวณจากค่า Settings ในแท็บ Summary · ตัวคูณ = 1 เดือน · อัปเดต % คอมมิชชันที่ Summary แล้ว ทุกช่องจะอัปเดตอัตโนมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1548,52 +1698,52 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SCENARIO A — ต้นทุน 0.11 บ./สลิป</t>
+          <t>SCENARIO A — ต้นทุนจากค่า Settings</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>SCENARIO B — ต้นทุน 0.077 บ./สลิป</t>
+          <t>SCENARIO B — ต้นทุนจากค่า Settings</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -1615,42 +1765,42 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost A</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GP A</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Comm @3%</t>
+          <t>Comm A</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Net GP</t>
+          <t>Net GP A</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost B</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GP B</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Comm @8%</t>
+          <t>Comm B</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Net GP</t>
+          <t>Net GP B</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1813,41 @@
       <c r="B6" s="20" t="n">
         <v>100000</v>
       </c>
-      <c r="C6" s="20" t="n">
-        <v>12500</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>11000</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>375</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>1125</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>7700</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>4800</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>3800</v>
+      <c r="C6" s="20">
+        <f>B6*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>B6*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="21">
+        <f>C6*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G6" s="21">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="22">
+        <f>B6*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>C6-H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>C6*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K6" s="22">
+        <f>I6-J6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1700,32 +1859,41 @@
       <c r="B7" s="20" t="n">
         <v>200000</v>
       </c>
-      <c r="C7" s="20" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>22000</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>750</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>2250</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>15400</v>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>9600</v>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>7600</v>
+      <c r="C7" s="20">
+        <f>B7*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>B7*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>C7*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="22">
+        <f>B7*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I7" s="22">
+        <f>C7-H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>C7*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K7" s="22">
+        <f>I7-J7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1737,32 +1905,41 @@
       <c r="B8" s="20" t="n">
         <v>300000</v>
       </c>
-      <c r="C8" s="20" t="n">
-        <v>37500</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>33000</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>1125</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>3375</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>23100</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>14400</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>3000</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>11400</v>
+      <c r="C8" s="20">
+        <f>B8*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>B8*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>C8*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="22">
+        <f>B8*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>C8-H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>C8*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K8" s="22">
+        <f>I8-J8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1774,32 +1951,41 @@
       <c r="B9" s="20" t="n">
         <v>400000</v>
       </c>
-      <c r="C9" s="20" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>44000</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>30800</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>19200</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>15200</v>
+      <c r="C9" s="20">
+        <f>B9*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>B9*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>C9*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="22">
+        <f>B9*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>C9-H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>C9*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K9" s="22">
+        <f>I9-J9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1811,32 +1997,41 @@
       <c r="B10" s="20" t="n">
         <v>500000</v>
       </c>
-      <c r="C10" s="20" t="n">
-        <v>62500</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>55000</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>7500</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>1875</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>5625</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>38500</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>24000</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>19000</v>
+      <c r="C10" s="20">
+        <f>B10*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>B10*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>C10*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="22">
+        <f>B10*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>C10-H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>C10*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K10" s="22">
+        <f>I10-J10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1848,32 +2043,41 @@
       <c r="B11" s="20" t="n">
         <v>600000</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <v>75000</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>66000</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>6750</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>46200</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>28800</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>6000</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>22800</v>
+      <c r="C11" s="20">
+        <f>B11*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>B11*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>C11*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="22">
+        <f>B11*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I11" s="22">
+        <f>C11-H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>C11*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K11" s="22">
+        <f>I11-J11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1885,32 +2089,41 @@
       <c r="B12" s="20" t="n">
         <v>700000</v>
       </c>
-      <c r="C12" s="20" t="n">
-        <v>87500</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>77000</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>10500</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>2625</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>7875</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>53900</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>33600</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>7000</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>26600</v>
+      <c r="C12" s="20">
+        <f>B12*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>B12*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>C12*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="22">
+        <f>B12*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>C12-H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>C12*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K12" s="22">
+        <f>I12-J12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1922,32 +2135,41 @@
       <c r="B13" s="20" t="n">
         <v>800000</v>
       </c>
-      <c r="C13" s="20" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>88000</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>3000</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>9000</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>61600</v>
-      </c>
-      <c r="I13" s="22" t="n">
-        <v>38400</v>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>8000</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>30400</v>
+      <c r="C13" s="20">
+        <f>B13*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>B13*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>C13*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="22">
+        <f>B13*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>C13-H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>C13*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K13" s="22">
+        <f>I13-J13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1959,32 +2181,41 @@
       <c r="B14" s="20" t="n">
         <v>900000</v>
       </c>
-      <c r="C14" s="20" t="n">
-        <v>112500</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>99000</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>13500</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>3375</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>10125</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>69300</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>43200</v>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>9000</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>34200</v>
+      <c r="C14" s="20">
+        <f>B14*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>B14*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>C14*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="22">
+        <f>B14*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I14" s="22">
+        <f>C14-H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="22">
+        <f>C14*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K14" s="22">
+        <f>I14-J14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1996,32 +2227,41 @@
       <c r="B15" s="20" t="n">
         <v>1000000</v>
       </c>
-      <c r="C15" s="20" t="n">
-        <v>125000</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>110000</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>3750</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>11250</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>77000</v>
-      </c>
-      <c r="I15" s="22" t="n">
-        <v>48000</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <v>38000</v>
+      <c r="C15" s="20">
+        <f>B15*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>B15*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>C15*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="22">
+        <f>B15*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I15" s="22">
+        <f>C15-H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="22">
+        <f>C15*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K15" s="22">
+        <f>I15-J15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2030,37 +2270,48 @@
           <t>รวม</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <v>687500</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <v>605000</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>82500</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>20625</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>61875</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>423500</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>264000</v>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>55000</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>209000</v>
-      </c>
-    </row>
+      <c r="B16" s="24">
+        <f>SUM(B6:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>SUM(C6:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>SUM(D6:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>SUM(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>SUM(F6:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="24">
+        <f>SUM(G6:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="24">
+        <f>SUM(H6:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="24">
+        <f>SUM(I6:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="24">
+        <f>SUM(J6:J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="24">
+        <f>SUM(K6:K15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -2069,52 +2320,52 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2131,12 +2382,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -2146,32 +2397,32 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2181,54 +2432,54 @@
           <t>Package</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>ระดับแพ็กเกจ MOU (Coperate A → J) ตามจำนวนสลิปที่ลูกค้าซื้อ</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2238,54 +2489,54 @@
           <t>Slips/1 Month</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>base × 1</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>จำนวนสลิปทั้งหมดในรอบสัญญา · J = 1,000,000</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2295,54 +2546,54 @@
           <t>Price/1 Month</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Slips × 0.125</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>รายได้รวมที่ EasySlip รับจากลูกค้า · J = 125,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>รายได้รวมที่ EasySlip รับจากลูกค้า · J = 125,000 บาท</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2352,54 +2603,54 @@
           <t>Cost (A)</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Slips × 0.11</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>ต้นทุนรวมที่จ่าย KBank (Scenario A) · J = 110,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>ต้นทุนรวมที่จ่าย KBank (Scenario A) · J = 110,000 บาท</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2409,54 +2660,54 @@
           <t>GP (A)</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Price − Cost (A)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น Scenario A · J = 15,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario A · J = 15,000 บาท</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2466,54 +2717,54 @@
           <t>Comm @3%</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Price × 0.03</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>ค่าคอมเซลส์ Scenario A · J = 3,750 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>ค่าคอมมิชชันเซลส์ Scenario A · J = 3,750 บาท</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2523,54 +2774,54 @@
           <t>Net GP (A)</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>GP − Comm</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>กำไรสุทธิหลังหักคอม Scenario A · J = 11,250 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอมมิชชัน Scenario A · J = 11,250 บาท</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2580,54 +2831,54 @@
           <t>Cost (B)</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Slips × 0.077</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>ต้นทุน Scenario B (mix blend) · J = 77,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario B (ส่วนผสม) · J = 77,000 บาท</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2637,54 +2888,54 @@
           <t>GP (B)</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Price − Cost (B)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น Scenario B · J = 48,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario B · J = 48,000 บาท</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2694,54 +2945,54 @@
           <t>Comm @8%</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Price × 0.08</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>ค่าคอมเซลส์ Scenario B · J = 10,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>ค่าคอมมิชชันเซลส์ Scenario B · J = 10,000 บาท</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2751,54 +3002,54 @@
           <t>Net GP (B)</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>GP − Comm</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>กำไรสุทธิหลังหักคอม Scenario B · J = 38,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอมมิชชัน Scenario B · J = 38,000 บาท</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2808,57 +3059,58 @@
           <t>รวม (Total)</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>SUM(A–J)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>ผลรวมทุก tier ใช้ดูเพดานยอดรวมถ้าขายได้ครบทุกแพ็ก</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -2867,52 +3119,52 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2922,54 +3174,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Scenario A = ลูกค้าใช้ Other-source 100% (worst case) — margin บาง ค่าคอม 3%</t>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Scenario A = ลูกค้าใช้ Other-source 100% (กรณีที่เลวร้ายที่สุด) — อัตรากำไรบาง ค่าคอมมิชชัน 3%</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -2979,54 +3231,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>Scenario B = mix blend ~30/70 — margin หนา ค่าคอม 8%</t>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Scenario B = ส่วนผสม ~30/70 — อัตรากำไรหนา ค่าคอมมิชชัน 8%</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3036,54 +3288,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>ค่าใน Net GP คือกำไรหลังหักคอมแล้ว ยังไม่หัก opex บริษัท</t>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>ค่าใน Net GP คือกำไรหลังหักค่าคอมมิชชันแล้ว ยังไม่หักค่าใช้จ่ายของบริษัท</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3093,54 +3345,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>ถ้าลูกค้าซื้อจำนวนสลิปนอกตาราง → เปิดแท็บ Per-Slip Detail คำนวณเอง</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3186,6 +3438,9 @@
     <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:ZZ1000" calculatedColumn="1" emptyCellReference="1" evalError="1" formula="1" formulaRange="1" listDataValidation="1" numberStoredAsText="1" twoDigitTextYear="1" unlockedFormula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -3227,10 +3482,11 @@
     <row r="2" ht="22" customHeight="1">
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ราคาขาย flat 0.125 บ./สลิป · ตัวเลขเป็นบาททั้งหมด · multiplier = 12 เดือน</t>
-        </is>
-      </c>
-    </row>
+          <t>ตัวเลขทั้งหมดคำนวณจากค่า Settings ในแท็บ Summary · ตัวคูณ = 12 เดือน · อัปเดต % คอมมิชชันที่ Summary แล้ว ทุกช่องจะอัปเดตอัตโนมัติ</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3239,52 +3495,52 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>SCENARIO A — ต้นทุน 0.11 บ./สลิป</t>
+          <t>SCENARIO A — ต้นทุนจากค่า Settings</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>SCENARIO B — ต้นทุน 0.077 บ./สลิป</t>
+          <t>SCENARIO B — ต้นทุนจากค่า Settings</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3306,42 +3562,42 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost A</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GP A</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Comm @3%</t>
+          <t>Comm A</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Net GP</t>
+          <t>Net GP A</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Cost</t>
+          <t>Cost B</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>GP</t>
+          <t>GP B</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Comm @8%</t>
+          <t>Comm B</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Net GP</t>
+          <t>Net GP B</t>
         </is>
       </c>
     </row>
@@ -3354,32 +3610,41 @@
       <c r="B6" s="20" t="n">
         <v>1200000</v>
       </c>
-      <c r="C6" s="20" t="n">
-        <v>150000</v>
-      </c>
-      <c r="D6" s="21" t="n">
-        <v>132000</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>13500</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>92400</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>57600</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>12000</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>45600</v>
+      <c r="C6" s="20">
+        <f>B6*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
+        <f>B6*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="21">
+        <f>C6*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G6" s="21">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="22">
+        <f>B6*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I6" s="22">
+        <f>C6-H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>C6*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K6" s="22">
+        <f>I6-J6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -3391,32 +3656,41 @@
       <c r="B7" s="20" t="n">
         <v>2400000</v>
       </c>
-      <c r="C7" s="20" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>264000</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>36000</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>27000</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>184800</v>
-      </c>
-      <c r="I7" s="22" t="n">
-        <v>115200</v>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>24000</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>91200</v>
+      <c r="C7" s="20">
+        <f>B7*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D7" s="21">
+        <f>B7*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="21">
+        <f>C7*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G7" s="21">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="22">
+        <f>B7*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I7" s="22">
+        <f>C7-H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>C7*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K7" s="22">
+        <f>I7-J7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -3428,32 +3702,41 @@
       <c r="B8" s="20" t="n">
         <v>3600000</v>
       </c>
-      <c r="C8" s="20" t="n">
-        <v>450000</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <v>396000</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>54000</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>13500</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>40500</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>277200</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>172800</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>36000</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>136800</v>
+      <c r="C8" s="20">
+        <f>B8*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>B8*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="21">
+        <f>C8*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G8" s="21">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="22">
+        <f>B8*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I8" s="22">
+        <f>C8-H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>C8*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K8" s="22">
+        <f>I8-J8</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -3465,32 +3748,41 @@
       <c r="B9" s="20" t="n">
         <v>4800000</v>
       </c>
-      <c r="C9" s="20" t="n">
-        <v>600000</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <v>528000</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>54000</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>369600</v>
-      </c>
-      <c r="I9" s="22" t="n">
-        <v>230400</v>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>48000</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>182400</v>
+      <c r="C9" s="20">
+        <f>B9*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D9" s="21">
+        <f>B9*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>C9*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G9" s="21">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="22">
+        <f>B9*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I9" s="22">
+        <f>C9-H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>C9*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K9" s="22">
+        <f>I9-J9</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -3502,32 +3794,41 @@
       <c r="B10" s="20" t="n">
         <v>6000000</v>
       </c>
-      <c r="C10" s="20" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>660000</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>90000</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>22500</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>67500</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>462000</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>288000</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>60000</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>228000</v>
+      <c r="C10" s="20">
+        <f>B10*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>B10*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>C10*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="22">
+        <f>B10*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I10" s="22">
+        <f>C10-H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>C10*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K10" s="22">
+        <f>I10-J10</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -3539,32 +3840,41 @@
       <c r="B11" s="20" t="n">
         <v>7200000</v>
       </c>
-      <c r="C11" s="20" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>792000</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>108000</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>27000</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>81000</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>554400</v>
-      </c>
-      <c r="I11" s="22" t="n">
-        <v>345600</v>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>72000</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>273600</v>
+      <c r="C11" s="20">
+        <f>B11*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
+        <f>B11*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
+        <f>C11-D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>C11*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G11" s="21">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="22">
+        <f>B11*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I11" s="22">
+        <f>C11-H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>C11*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K11" s="22">
+        <f>I11-J11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3576,32 +3886,41 @@
       <c r="B12" s="20" t="n">
         <v>8400000</v>
       </c>
-      <c r="C12" s="20" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>924000</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>126000</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>31500</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>94500</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>646800</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>403200</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>84000</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>319200</v>
+      <c r="C12" s="20">
+        <f>B12*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>B12*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>C12-D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>C12*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="22">
+        <f>B12*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I12" s="22">
+        <f>C12-H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>C12*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K12" s="22">
+        <f>I12-J12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -3613,32 +3932,41 @@
       <c r="B13" s="20" t="n">
         <v>9600000</v>
       </c>
-      <c r="C13" s="20" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D13" s="21" t="n">
-        <v>1056000</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>144000</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>36000</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>108000</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>739200</v>
-      </c>
-      <c r="I13" s="22" t="n">
-        <v>460800</v>
-      </c>
-      <c r="J13" s="22" t="n">
-        <v>96000</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>364800</v>
+      <c r="C13" s="20">
+        <f>B13*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>B13*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>C13-D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>C13*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G13" s="21">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="22">
+        <f>B13*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I13" s="22">
+        <f>C13-H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>C13*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K13" s="22">
+        <f>I13-J13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3650,32 +3978,41 @@
       <c r="B14" s="20" t="n">
         <v>10800000</v>
       </c>
-      <c r="C14" s="20" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>1188000</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>162000</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>40500</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>121500</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>831600</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>518400</v>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>108000</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>410400</v>
+      <c r="C14" s="20">
+        <f>B14*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>B14*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>C14-D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>C14*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G14" s="21">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="22">
+        <f>B14*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I14" s="22">
+        <f>C14-H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="22">
+        <f>C14*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K14" s="22">
+        <f>I14-J14</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -3687,32 +4024,41 @@
       <c r="B15" s="20" t="n">
         <v>12000000</v>
       </c>
-      <c r="C15" s="20" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>1320000</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>180000</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>45000</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>135000</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>924000</v>
-      </c>
-      <c r="I15" s="22" t="n">
-        <v>576000</v>
-      </c>
-      <c r="J15" s="22" t="n">
-        <v>120000</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <v>456000</v>
+      <c r="C15" s="20">
+        <f>B15*Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>B15*Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
+        <f>C15-D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>C15*Summary!$B$9</f>
+        <v/>
+      </c>
+      <c r="G15" s="21">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="22">
+        <f>B15*Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="I15" s="22">
+        <f>C15-H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="22">
+        <f>C15*Summary!$B$10</f>
+        <v/>
+      </c>
+      <c r="K15" s="22">
+        <f>I15-J15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3721,37 +4067,48 @@
           <t>รวม</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="C16" s="24" t="n">
-        <v>8250000</v>
-      </c>
-      <c r="D16" s="24" t="n">
-        <v>7260000</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>990000</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>247500</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>742500</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>5082000</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>3168000</v>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>660000</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>2508000</v>
-      </c>
-    </row>
+      <c r="B16" s="24">
+        <f>SUM(B6:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>SUM(C6:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>SUM(D6:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>SUM(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>SUM(F6:F15)</f>
+        <v/>
+      </c>
+      <c r="G16" s="24">
+        <f>SUM(G6:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="24">
+        <f>SUM(H6:H15)</f>
+        <v/>
+      </c>
+      <c r="I16" s="24">
+        <f>SUM(I6:I15)</f>
+        <v/>
+      </c>
+      <c r="J16" s="24">
+        <f>SUM(J6:J15)</f>
+        <v/>
+      </c>
+      <c r="K16" s="24">
+        <f>SUM(K6:K15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
@@ -3760,52 +4117,52 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3822,12 +4179,12 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -3837,32 +4194,32 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3872,54 +4229,54 @@
           <t>Package</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>ระดับแพ็กเกจ MOU (Coperate A → J) ตามจำนวนสลิปที่ลูกค้าซื้อ</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3929,54 +4286,54 @@
           <t>Slips/12 Month</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>base × 12</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>จำนวนสลิปทั้งหมดในรอบสัญญา · J = 12,000,000</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -3986,54 +4343,54 @@
           <t>Price/12 Month</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>Slips × 0.125</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>รายได้รวมที่ EasySlip รับจากลูกค้า · J = 1,500,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>รายได้รวมที่ EasySlip รับจากลูกค้า · J = 1,500,000 บาท</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4043,54 +4400,54 @@
           <t>Cost (A)</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>Slips × 0.11</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>ต้นทุนรวมที่จ่าย KBank (Scenario A) · J = 1,320,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>ต้นทุนรวมที่จ่าย KBank (Scenario A) · J = 1,320,000 บาท</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4100,54 +4457,54 @@
           <t>GP (A)</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>Price − Cost (A)</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น Scenario A · J = 180,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario A · J = 180,000 บาท</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4157,54 +4514,54 @@
           <t>Comm @3%</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Price × 0.03</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>ค่าคอมเซลส์ Scenario A · J = 45,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>ค่าคอมมิชชันเซลส์ Scenario A · J = 45,000 บาท</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4214,54 +4571,54 @@
           <t>Net GP (A)</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>GP − Comm</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>กำไรสุทธิหลังหักคอม Scenario A · J = 135,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอมมิชชัน Scenario A · J = 135,000 บาท</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4271,54 +4628,54 @@
           <t>Cost (B)</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>Slips × 0.077</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>ต้นทุน Scenario B (mix blend) · J = 924,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>ต้นทุน Scenario B (ส่วนผสม) · J = 924,000 บาท</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4328,54 +4685,54 @@
           <t>GP (B)</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>Price − Cost (B)</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>กำไรขั้นต้น Scenario B · J = 576,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>กำไรขั้นต้น Scenario B · J = 576,000 บาท</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4385,54 +4742,54 @@
           <t>Comm @8%</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Price × 0.08</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>ค่าคอมเซลส์ Scenario B · J = 120,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>ค่าคอมมิชชันเซลส์ Scenario B · J = 120,000 บาท</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4442,54 +4799,54 @@
           <t>Net GP (B)</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>GP − Comm</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E30" s="18" t="inlineStr">
-        <is>
-          <t>กำไรสุทธิหลังหักคอม Scenario B · J = 456,000 บ.</t>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>กำไรสุทธิหลังหักคอมมิชชัน Scenario B · J = 456,000 บาท</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4499,57 +4856,58 @@
           <t>รวม (Total)</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>SUM(A–J)</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E31" s="18" t="inlineStr">
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>ผลรวมทุก tier ใช้ดูเพดานยอดรวมถ้าขายได้ครบทุกแพ็ก</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
@@ -4558,52 +4916,52 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4613,54 +4971,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>Scenario A = ลูกค้าใช้ Other-source 100% (worst case) — margin บาง ค่าคอม 3%</t>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Scenario A = ลูกค้าใช้ Other-source 100% (กรณีที่เลวร้ายที่สุด) — อัตรากำไรบาง ค่าคอมมิชชัน 3%</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4670,54 +5028,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>Scenario B = mix blend ~30/70 — margin หนา ค่าคอม 8%</t>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Scenario B = ส่วนผสม ~30/70 — อัตรากำไรหนา ค่าคอมมิชชัน 8%</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4727,54 +5085,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>ค่าใน Net GP คือกำไรหลังหักคอมแล้ว ยังไม่หัก opex บริษัท</t>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>ค่าใน Net GP คือกำไรหลังหักค่าคอมมิชชันแล้ว ยังไม่หักค่าใช้จ่ายของบริษัท</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4784,54 +5142,54 @@
           <t>•</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>ถ้าลูกค้าซื้อจำนวนสลิปนอกตาราง → เปิดแท็บ Per-Slip Detail คำนวณเอง</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4877,6 +5235,9 @@
     <mergeCell ref="D4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:ZZ1000" calculatedColumn="1" emptyCellReference="1" evalError="1" formula="1" formulaRange="1" listDataValidation="1" numberStoredAsText="1" twoDigitTextYear="1" unlockedFormula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -4912,34 +5273,35 @@
     <row r="2" ht="22" customHeight="1">
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ค่าคอม/สลิป (ใช้ประมาณการเร็วๆ สำหรับ tier ที่ไม่ตรงตาราง)</t>
-        </is>
-      </c>
-    </row>
+          <t>ค่าคอมมิชชัน/สลิป (ใช้ประมาณการเบื้องต้นสำหรับ tier ที่ไม่ตรงตาราง)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>ค่าคอม / สลิป — ทั้งสอง Scenario</t>
+          <t>ค่าคอมมิชชัน / สลิป — ทั้งสอง Scenario</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -4976,16 +5338,18 @@
           <t>ราคาขาย/สลิป</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
-        <v>0.125</v>
+      <c r="B6" s="14">
+        <f>Summary!$B$6</f>
+        <v/>
       </c>
       <c r="C6" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
-        <v>0.125</v>
+      <c r="D6" s="17">
+        <f>Summary!$B$6</f>
+        <v/>
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
@@ -4999,16 +5363,18 @@
           <t>ต้นทุน/สลิป</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v>0.11</v>
+      <c r="B7" s="14">
+        <f>Summary!$B$7</f>
+        <v/>
       </c>
       <c r="C7" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>0.077</v>
+      <c r="D7" s="17">
+        <f>Summary!$B$8</f>
+        <v/>
       </c>
       <c r="E7" s="27" t="inlineStr">
         <is>
@@ -5022,16 +5388,18 @@
           <t>GP/สลิป</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>0.015</v>
+      <c r="B8" s="14">
+        <f>Summary!$B$6-Summary!$B$7</f>
+        <v/>
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>0.048</v>
+      <c r="D8" s="17">
+        <f>Summary!$B$6-Summary!$B$8</f>
+        <v/>
       </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
@@ -5045,16 +5413,18 @@
           <t>GP %</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
-        <v>0.12</v>
+      <c r="B9" s="15">
+        <f>(Summary!$B$6-Summary!$B$7)/Summary!$B$6</f>
+        <v/>
       </c>
       <c r="C9" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>0.384</v>
+      <c r="D9" s="18">
+        <f>(Summary!$B$6-Summary!$B$8)/Summary!$B$6</f>
+        <v/>
       </c>
       <c r="E9" s="27" t="inlineStr">
         <is>
@@ -5068,16 +5438,18 @@
           <t>เรทคอม (% revenue)</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>0.03</v>
+      <c r="B10" s="15">
+        <f>Summary!$B$9</f>
+        <v/>
       </c>
       <c r="C10" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>0.08</v>
+      <c r="D10" s="18">
+        <f>Summary!$B$10</f>
+        <v/>
       </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
@@ -5091,16 +5463,18 @@
           <t>ค่าคอม/สลิป</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>0.00375</v>
+      <c r="B11" s="14">
+        <f>Summary!$B$6*Summary!$B$9</f>
+        <v/>
       </c>
       <c r="C11" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
-        <v>0.01</v>
+      <c r="D11" s="17">
+        <f>Summary!$B$6*Summary!$B$10</f>
+        <v/>
       </c>
       <c r="E11" s="27" t="inlineStr">
         <is>
@@ -5114,16 +5488,18 @@
           <t>Net GP/สลิป</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
-        <v>0.01125</v>
+      <c r="B12" s="14">
+        <f>Summary!$B$6-Summary!$B$7-Summary!$B$6*Summary!$B$9</f>
+        <v/>
       </c>
       <c r="C12" s="26" t="inlineStr">
         <is>
           <t>บ.</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
-        <v>0.038</v>
+      <c r="D12" s="17">
+        <f>Summary!$B$6-Summary!$B$8-Summary!$B$6*Summary!$B$10</f>
+        <v/>
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
@@ -5137,16 +5513,18 @@
           <t>Net margin %</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>0.09</v>
+      <c r="B13" s="15">
+        <f>(Summary!$B$6-Summary!$B$7-Summary!$B$6*Summary!$B$9)/Summary!$B$6</f>
+        <v/>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>0.304</v>
+      <c r="D13" s="18">
+        <f>(Summary!$B$6-Summary!$B$8-Summary!$B$6*Summary!$B$10)/Summary!$B$6</f>
+        <v/>
       </c>
       <c r="E13" s="27" t="inlineStr">
         <is>
@@ -5154,6 +5532,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -5162,49 +5541,49 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>เมื่อไรใช้</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>ลูกค้าซื้อจำนวนสลิปที่ไม่ตรงตาราง 1 Month / 12 Month (เช่น 250,000 สลิป) ใช้ค่าใน "ค่าคอม/สลิป" คูณกับจำนวนสลิปที่ขายได้</t>
+          <t>เมื่อไหร่ควรใช้</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>ลูกค้าซื้อจำนวนสลิปที่ไม่ตรงตาราง 1 เดือน / 12 เดือน (เช่น 250,000 สลิป) ใช้ค่าใน "ค่าคอม/สลิป" คูณกับจำนวนสลิปที่ขายได้</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -5214,24 +5593,24 @@
           <t>ตัวอย่าง Scenario A</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>ลูกค้าซื้อ 250,000 สลิป → ค่าคอม = 250,000 × 0.00375 = 937.50 บ. · บริษัทเหลือ Net GP = 250,000 × 0.011 = 2,750 บ.</t>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>ลูกค้าซื้อ 250,000 สลิป → ค่าคอมมิชชัน = 250,000 × 0.00375 = 937.50 บาท · บริษัทเหลือ Net GP = 250,000 × 0.011 = 2,750 บาท</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -5241,51 +5620,51 @@
           <t>ตัวอย่าง Scenario B</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>ลูกค้าซื้อ 250,000 สลิป → ค่าคอม = 250,000 × 0.01 = 2,500 บ. · บริษัทเหลือ Net GP = 250,000 × 0.038 = 9,500 บ.</t>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>ลูกค้าซื้อ 250,000 สลิป → ค่าคอมมิชชัน = 250,000 × 0.01 = 2,500 บาท · บริษัทเหลือ Net GP = 250,000 × 0.038 = 9,500 บาท</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>เลือก Scenario ยังไง</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>ถ้าไม่รู้ traffic mix → ใช้ A เพื่อ safe · ถ้า lock mix K-src ≥ 30% ใน MOU → ใช้ B</t>
+          <t>เลือก Scenario อย่างไร</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>ถ้าไม่ทราบ traffic mix → ใช้ A เพื่อความปลอดภัย · ถ้า lock mix K-src ≥ 30% ใน MOU → ใช้ B</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t> </t>
+          <t> </t>
         </is>
       </c>
     </row>
@@ -5302,5 +5681,8 @@
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:ZZ1000" calculatedColumn="1" emptyCellReference="1" evalError="1" formula="1" formulaRange="1" listDataValidation="1" numberStoredAsText="1" twoDigitTextYear="1" unlockedFormula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
+++ b/Thunder Solution/Reports/thunder-corporate-api-commission.xlsx
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -817,86 +817,86 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>อัตราค่าคอมมิชชัน Scenario A</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
+    <row r="9"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>🎚️ อัตราค่าคอมมิชชันแยกตาม Coperate — แก้ % รายแพ็กในช่องเหลืองได้เลย</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Rate A (%)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Rate B (%)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>หมายเหตุ</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Coperate A</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
         <v>0.03</v>
       </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>% ของรายได้ที่จ่ายให้เซลส์ (ใช้กับ Scenario A)</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>อัตราค่าคอมมิชชัน Scenario B</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
+      <c r="C12" s="12" t="n">
         <v>0.08</v>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>% ของรายได้ที่จ่ายให้เซลส์ (ใช้กับ Scenario B)</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>เปรียบเทียบ Scenario ต้นทุน (อ้างอิงจากค่า Settings ด้านบน)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t> </t>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>แต่ละแพ็กแก้ % แยกได้ ถ้าอยากให้ทุกแพ็กเท่ากันก็ใส่เลขเดียวกัน</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -911,257 +911,127 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>ต้นทุน/สลิป</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>GP/สลิป</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>GP %</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>เรทคอมแนะนำ</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Net margin หลังคอม</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Coperate B</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>A — แหล่ง Other-source 100%</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>Summary!$B$7</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>Summary!$B$6-Summary!$B$7</f>
-        <v/>
-      </c>
-      <c r="D14" s="15">
-        <f>(Summary!$B$6-Summary!$B$7)/Summary!$B$6</f>
-        <v/>
-      </c>
-      <c r="E14" s="15">
-        <f>Summary!$B$9</f>
-        <v/>
-      </c>
-      <c r="F14" s="15">
-        <f>(Summary!$B$6-Summary!$B$7-Summary!$B$6*Summary!$B$9)/Summary!$B$6</f>
-        <v/>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Coperate C</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>B — ส่วนผสม (~30/70)</t>
-        </is>
-      </c>
-      <c r="B15" s="17">
-        <f>Summary!$B$8</f>
-        <v/>
-      </c>
-      <c r="C15" s="17">
-        <f>Summary!$B$6-Summary!$B$8</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>(Summary!$B$6-Summary!$B$8)/Summary!$B$6</f>
-        <v/>
-      </c>
-      <c r="E15" s="18">
-        <f>Summary!$B$10</f>
-        <v/>
-      </c>
-      <c r="F15" s="18">
-        <f>(Summary!$B$6-Summary!$B$8-Summary!$B$6*Summary!$B$10)/Summary!$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>แนวคิดอัตราค่าคอมมิชชัน</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Coperate D</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Coperate E</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Coperate F</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Scenario A (ต้นทุน 0.11)</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>อัตรากำไรบาง (12%) → ให้ค่าคอม 3% ของรายได้ บริษัทเหลือ ~9% รองรับค่าใช้จ่าย</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
+          <t>Coperate G</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Scenario B (ต้นทุน 0.077)</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>อัตรากำไรหนา (38.4%) → ให้ค่าคอม 8% ของรายได้ บริษัทเหลือ ~30% เซลส์ได้ผลตอบแทนดี</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
+          <t>Coperate H</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>ทางเลือก: คิดเป็น % ของกำไรขั้นต้น</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>A @ 25% ของกำไรขั้นต้น ≈ 3% ของรายได้ · B @ 20% ของกำไรขั้นต้น ≈ 7.7% ของรายได้</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
+          <t>Coperate I</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>ข้อระวัง MOU</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>ถ้าใช้ Scenario B ต้อง lock traffic mix ใน MOU (เช่น K-src ≥ 30%)</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
+          <t>Coperate J</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>⚡ วิธีใช้งานอย่างรวดเร็ว (Sales Playbook)</t>
+          <t>เปรียบเทียบ Scenario ต้นทุน (อ้างอิงจากค่า Settings ด้านบน)</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1193,451 +1063,732 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>ต้นทุน/สลิป</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>GP/สลิป</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>GP %</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>เรทเฉลี่ย (A–J)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Net margin หลังค่าคอมเฉลี่ย</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>A — แหล่ง Other-source 100%</t>
+        </is>
+      </c>
+      <c r="B25" s="14">
+        <f>Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="C25" s="14">
+        <f>Summary!$B$6-Summary!$B$7</f>
+        <v/>
+      </c>
+      <c r="D25" s="15">
+        <f>(Summary!$B$6-Summary!$B$7)/Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="E25" s="15">
+        <f>AVERAGE(Summary!$B$12:$B$21)</f>
+        <v/>
+      </c>
+      <c r="F25" s="15">
+        <f>(Summary!$B$6-Summary!$B$7-Summary!$B$6*AVERAGE(Summary!$B$12:$B$21))/Summary!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>B — ส่วนผสม (~30/70)</t>
+        </is>
+      </c>
+      <c r="B26" s="17">
+        <f>Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="C26" s="17">
+        <f>Summary!$B$6-Summary!$B$8</f>
+        <v/>
+      </c>
+      <c r="D26" s="18">
+        <f>(Summary!$B$6-Summary!$B$8)/Summary!$B$6</f>
+        <v/>
+      </c>
+      <c r="E26" s="18">
+        <f>AVERAGE(Summary!$C$12:$C$21)</f>
+        <v/>
+      </c>
+      <c r="F26" s="18">
+        <f>(Summary!$B$6-Summary!$B$8-Summary!$B$6*AVERAGE(Summary!$C$12:$C$21))/Summary!$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>แนวคิดอัตราค่าคอมมิชชัน</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Scenario A (ต้นทุน 0.11)</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>อัตรากำไรบาง (12%) → ให้ค่าคอม 3% ของรายได้ บริษัทเหลือ ~9% รองรับค่าใช้จ่าย</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Scenario B (ต้นทุน 0.077)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>อัตรากำไรหนา (38.4%) → ให้ค่าคอม 8% ของรายได้ บริษัทเหลือ ~30% เซลส์ได้ผลตอบแทนดี</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>ทางเลือก: คิดเป็น % ของกำไรขั้นต้น</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>A @ 25% ของกำไรขั้นต้น ≈ 3% ของรายได้ · B @ 20% ของกำไรขั้นต้น ≈ 7.7% ของรายได้</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>ข้อระวัง MOU</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>ถ้าใช้ Scenario B ต้อง lock traffic mix ใน MOU (เช่น K-src ≥ 30%)</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>⚡ วิธีใช้งานอย่างรวดเร็ว (Sales Playbook)</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>ทำอะไร</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>ตรวจสอบก่อน: ลูกค้ามี traffic เป็น K-src/Other เท่าไร — ถ้าไม่ทราบ → ใช้ Scenario A เพื่อความปลอดภัย</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>สอบถามงบประมาณของลูกค้า → ตรวจสอบว่าตรงกับ Coperate ตัวไหน (เปิดแท็บ 1 เดือน หรือ 12 เดือน)</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>อ่านช่อง Comm ของ Scenario ที่ใช้ → คือยอดที่เซลส์จะได้รับ</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>ตรวจสอบช่อง Net GP → ดูว่าบริษัทเหลือกำไรเท่าไรหลังจ่ายค่าคอมมิชชัน</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>ถ้าใช้ Scenario B ต้องเขียนใน MOU: ลูกค้ารับประกัน K-src ≥ 30%</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>ถ้า tier ของลูกค้าไม่อยู่ในตาราง (เช่น 250,000 สลิป) → ใช้แท็บ Per-Slip Detail คูณเอง</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>⚠️ ข้อควรระวัง</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>หัวข้อ</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>รายละเอียด</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>ราคาขายคงที่ 0.125</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>ไม่ใช่ส่วนลดตาม tier เหมือนแพ็กเกจมาตรฐาน — ทุกระดับจ่าย 0.125 บาท/สลิปเท่ากัน ดังนั้นแพ็กใหญ่จึงไม่ได้กำไรเพิ่ม % ต่างจาก Web Pricing</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>ต้นทุน 0.077 ไม่ใช่ค่ามาตรฐาน</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>เป็นค่าประมาณกรณีส่วนผสม 30/70 ลูกค้าจริงต้องตรวจสอบ traffic mix ก่อน — ถ้าใช้ Other เกิน 70% ต้นทุนจะเกิน 0.077 ทันที</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>Net GP ≠ Net Profit</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Net GP ในไฟล์นี้ = หลังหักค่าคอมมิชชันแล้ว แต่ยังไม่หักค่าใช้จ่าย (server, dev, support, sales operation) — ของจริงเหลือน้อยกว่านี้อีก 10–20%</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>VAT</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>ตัวเลขในไฟล์เป็นราคาคงที่ตาม MOU (ราคาที่แสดงในตารางลูกค้า) ไม่ได้แยก excl/incl VAT — ถ้าจะใช้คำนวณงบจริง ปรึกษาฝ่ายบัญชี</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t> </t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A12:F12"/>
+  <mergeCells count="31">
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="D7:F7"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="D12:F12"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="D8:F8"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="D5:F5"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B38:F38"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B32:F32"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="D6:F6"/>
-    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1826,7 +1977,7 @@
         <v/>
       </c>
       <c r="F6" s="21">
-        <f>C6*Summary!$B$9</f>
+        <f>C6*Summary!$B$12</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -1842,7 +1993,7 @@
         <v/>
       </c>
       <c r="J6" s="22">
-        <f>C6*Summary!$B$10</f>
+        <f>C6*Summary!$C$12</f>
         <v/>
       </c>
       <c r="K6" s="22">
@@ -1872,7 +2023,7 @@
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>C7*Summary!$B$9</f>
+        <f>C7*Summary!$B$13</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -1888,7 +2039,7 @@
         <v/>
       </c>
       <c r="J7" s="22">
-        <f>C7*Summary!$B$10</f>
+        <f>C7*Summary!$C$13</f>
         <v/>
       </c>
       <c r="K7" s="22">
@@ -1918,7 +2069,7 @@
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>C8*Summary!$B$9</f>
+        <f>C8*Summary!$B$14</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -1934,7 +2085,7 @@
         <v/>
       </c>
       <c r="J8" s="22">
-        <f>C8*Summary!$B$10</f>
+        <f>C8*Summary!$C$14</f>
         <v/>
       </c>
       <c r="K8" s="22">
@@ -1964,7 +2115,7 @@
         <v/>
       </c>
       <c r="F9" s="21">
-        <f>C9*Summary!$B$9</f>
+        <f>C9*Summary!$B$15</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -1980,7 +2131,7 @@
         <v/>
       </c>
       <c r="J9" s="22">
-        <f>C9*Summary!$B$10</f>
+        <f>C9*Summary!$C$15</f>
         <v/>
       </c>
       <c r="K9" s="22">
@@ -2010,7 +2161,7 @@
         <v/>
       </c>
       <c r="F10" s="21">
-        <f>C10*Summary!$B$9</f>
+        <f>C10*Summary!$B$16</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -2026,7 +2177,7 @@
         <v/>
       </c>
       <c r="J10" s="22">
-        <f>C10*Summary!$B$10</f>
+        <f>C10*Summary!$C$16</f>
         <v/>
       </c>
       <c r="K10" s="22">
@@ -2056,7 +2207,7 @@
         <v/>
       </c>
       <c r="F11" s="21">
-        <f>C11*Summary!$B$9</f>
+        <f>C11*Summary!$B$17</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -2072,7 +2223,7 @@
         <v/>
       </c>
       <c r="J11" s="22">
-        <f>C11*Summary!$B$10</f>
+        <f>C11*Summary!$C$17</f>
         <v/>
       </c>
       <c r="K11" s="22">
@@ -2102,7 +2253,7 @@
         <v/>
       </c>
       <c r="F12" s="21">
-        <f>C12*Summary!$B$9</f>
+        <f>C12*Summary!$B$18</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -2118,7 +2269,7 @@
         <v/>
       </c>
       <c r="J12" s="22">
-        <f>C12*Summary!$B$10</f>
+        <f>C12*Summary!$C$18</f>
         <v/>
       </c>
       <c r="K12" s="22">
@@ -2148,7 +2299,7 @@
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>C13*Summary!$B$9</f>
+        <f>C13*Summary!$B$19</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -2164,7 +2315,7 @@
         <v/>
       </c>
       <c r="J13" s="22">
-        <f>C13*Summary!$B$10</f>
+        <f>C13*Summary!$C$19</f>
         <v/>
       </c>
       <c r="K13" s="22">
@@ -2194,7 +2345,7 @@
         <v/>
       </c>
       <c r="F14" s="21">
-        <f>C14*Summary!$B$9</f>
+        <f>C14*Summary!$B$20</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -2210,7 +2361,7 @@
         <v/>
       </c>
       <c r="J14" s="22">
-        <f>C14*Summary!$B$10</f>
+        <f>C14*Summary!$C$20</f>
         <v/>
       </c>
       <c r="K14" s="22">
@@ -2240,7 +2391,7 @@
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>C15*Summary!$B$9</f>
+        <f>C15*Summary!$B$21</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -2256,7 +2407,7 @@
         <v/>
       </c>
       <c r="J15" s="22">
-        <f>C15*Summary!$B$10</f>
+        <f>C15*Summary!$C$21</f>
         <v/>
       </c>
       <c r="K15" s="22">
@@ -3623,7 +3774,7 @@
         <v/>
       </c>
       <c r="F6" s="21">
-        <f>C6*Summary!$B$9</f>
+        <f>C6*Summary!$B$12</f>
         <v/>
       </c>
       <c r="G6" s="21">
@@ -3639,7 +3790,7 @@
         <v/>
       </c>
       <c r="J6" s="22">
-        <f>C6*Summary!$B$10</f>
+        <f>C6*Summary!$C$12</f>
         <v/>
       </c>
       <c r="K6" s="22">
@@ -3669,7 +3820,7 @@
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>C7*Summary!$B$9</f>
+        <f>C7*Summary!$B$13</f>
         <v/>
       </c>
       <c r="G7" s="21">
@@ -3685,7 +3836,7 @@
         <v/>
       </c>
       <c r="J7" s="22">
-        <f>C7*Summary!$B$10</f>
+        <f>C7*Summary!$C$13</f>
         <v/>
       </c>
       <c r="K7" s="22">
@@ -3715,7 +3866,7 @@
         <v/>
       </c>
       <c r="F8" s="21">
-        <f>C8*Summary!$B$9</f>
+        <f>C8*Summary!$B$14</f>
         <v/>
       </c>
       <c r="G8" s="21">
@@ -3731,7 +3882,7 @@
         <v/>
       </c>
       <c r="J8" s="22">
-        <f>C8*Summary!$B$10</f>
+        <f>C8*Summary!$C$14</f>
         <v/>
       </c>
       <c r="K8" s="22">
@@ -3761,7 +3912,7 @@
         <v/>
       </c>
       <c r="F9" s="21">
-        <f>C9*Summary!$B$9</f>
+        <f>C9*Summary!$B$15</f>
         <v/>
       </c>
       <c r="G9" s="21">
@@ -3777,7 +3928,7 @@
         <v/>
       </c>
       <c r="J9" s="22">
-        <f>C9*Summary!$B$10</f>
+        <f>C9*Summary!$C$15</f>
         <v/>
       </c>
       <c r="K9" s="22">
@@ -3807,7 +3958,7 @@
         <v/>
       </c>
       <c r="F10" s="21">
-        <f>C10*Summary!$B$9</f>
+        <f>C10*Summary!$B$16</f>
         <v/>
       </c>
       <c r="G10" s="21">
@@ -3823,7 +3974,7 @@
         <v/>
       </c>
       <c r="J10" s="22">
-        <f>C10*Summary!$B$10</f>
+        <f>C10*Summary!$C$16</f>
         <v/>
       </c>
       <c r="K10" s="22">
@@ -3853,7 +4004,7 @@
         <v/>
       </c>
       <c r="F11" s="21">
-        <f>C11*Summary!$B$9</f>
+        <f>C11*Summary!$B$17</f>
         <v/>
       </c>
       <c r="G11" s="21">
@@ -3869,7 +4020,7 @@
         <v/>
       </c>
       <c r="J11" s="22">
-        <f>C11*Summary!$B$10</f>
+        <f>C11*Summary!$C$17</f>
         <v/>
       </c>
       <c r="K11" s="22">
@@ -3899,7 +4050,7 @@
         <v/>
       </c>
       <c r="F12" s="21">
-        <f>C12*Summary!$B$9</f>
+        <f>C12*Summary!$B$18</f>
         <v/>
       </c>
       <c r="G12" s="21">
@@ -3915,7 +4066,7 @@
         <v/>
       </c>
       <c r="J12" s="22">
-        <f>C12*Summary!$B$10</f>
+        <f>C12*Summary!$C$18</f>
         <v/>
       </c>
       <c r="K12" s="22">
@@ -3945,7 +4096,7 @@
         <v/>
       </c>
       <c r="F13" s="21">
-        <f>C13*Summary!$B$9</f>
+        <f>C13*Summary!$B$19</f>
         <v/>
       </c>
       <c r="G13" s="21">
@@ -3961,7 +4112,7 @@
         <v/>
       </c>
       <c r="J13" s="22">
-        <f>C13*Summary!$B$10</f>
+        <f>C13*Summary!$C$19</f>
         <v/>
       </c>
       <c r="K13" s="22">
@@ -3991,7 +4142,7 @@
         <v/>
       </c>
       <c r="F14" s="21">
-        <f>C14*Summary!$B$9</f>
+        <f>C14*Summary!$B$20</f>
         <v/>
       </c>
       <c r="G14" s="21">
@@ -4007,7 +4158,7 @@
         <v/>
       </c>
       <c r="J14" s="22">
-        <f>C14*Summary!$B$10</f>
+        <f>C14*Summary!$C$20</f>
         <v/>
       </c>
       <c r="K14" s="22">
@@ -4037,7 +4188,7 @@
         <v/>
       </c>
       <c r="F15" s="21">
-        <f>C15*Summary!$B$9</f>
+        <f>C15*Summary!$B$21</f>
         <v/>
       </c>
       <c r="G15" s="21">
@@ -4053,7 +4204,7 @@
         <v/>
       </c>
       <c r="J15" s="22">
-        <f>C15*Summary!$B$10</f>
+        <f>C15*Summary!$C$21</f>
         <v/>
       </c>
       <c r="K15" s="22">
@@ -5435,11 +5586,11 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>เรทคอม (% revenue)</t>
+          <t>เรทคอมเฉลี่ย</t>
         </is>
       </c>
       <c r="B10" s="15">
-        <f>Summary!$B$9</f>
+        <f>AVERAGE(Summary!$B$12:$B$21)</f>
         <v/>
       </c>
       <c r="C10" s="26" t="inlineStr">
@@ -5448,7 +5599,7 @@
         </is>
       </c>
       <c r="D10" s="18">
-        <f>Summary!$B$10</f>
+        <f>AVERAGE(Summary!$C$12:$C$21)</f>
         <v/>
       </c>
       <c r="E10" s="27" t="inlineStr">
@@ -5460,11 +5611,11 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>ค่าคอม/สลิป</t>
+          <t>ค่าคอม/สลิป (เฉลี่ย)</t>
         </is>
       </c>
       <c r="B11" s="14">
-        <f>Summary!$B$6*Summary!$B$9</f>
+        <f>Summary!$B$6*AVERAGE(Summary!$B$12:$B$21)</f>
         <v/>
       </c>
       <c r="C11" s="26" t="inlineStr">
@@ -5473,7 +5624,7 @@
         </is>
       </c>
       <c r="D11" s="17">
-        <f>Summary!$B$6*Summary!$B$10</f>
+        <f>Summary!$B$6*AVERAGE(Summary!$C$12:$C$21)</f>
         <v/>
       </c>
       <c r="E11" s="27" t="inlineStr">
@@ -5485,11 +5636,11 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Net GP/สลิป</t>
+          <t>Net GP/สลิป (เฉลี่ย)</t>
         </is>
       </c>
       <c r="B12" s="14">
-        <f>Summary!$B$6-Summary!$B$7-Summary!$B$6*Summary!$B$9</f>
+        <f>Summary!$B$6-Summary!$B$7-Summary!$B$6*AVERAGE(Summary!$B$12:$B$21)</f>
         <v/>
       </c>
       <c r="C12" s="26" t="inlineStr">
@@ -5498,7 +5649,7 @@
         </is>
       </c>
       <c r="D12" s="17">
-        <f>Summary!$B$6-Summary!$B$8-Summary!$B$6*Summary!$B$10</f>
+        <f>Summary!$B$6-Summary!$B$8-Summary!$B$6*AVERAGE(Summary!$C$12:$C$21)</f>
         <v/>
       </c>
       <c r="E12" s="27" t="inlineStr">
@@ -5514,7 +5665,7 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>(Summary!$B$6-Summary!$B$7-Summary!$B$6*Summary!$B$9)/Summary!$B$6</f>
+        <f>(Summary!$B$6-Summary!$B$7-Summary!$B$6*AVERAGE(Summary!$B$12:$B$21))/Summary!$B$6</f>
         <v/>
       </c>
       <c r="C13" s="26" t="inlineStr">
@@ -5523,7 +5674,7 @@
         </is>
       </c>
       <c r="D13" s="18">
-        <f>(Summary!$B$6-Summary!$B$8-Summary!$B$6*Summary!$B$10)/Summary!$B$6</f>
+        <f>(Summary!$B$6-Summary!$B$8-Summary!$B$6*AVERAGE(Summary!$C$12:$C$21))/Summary!$B$6</f>
         <v/>
       </c>
       <c r="E13" s="27" t="inlineStr">
